--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vng-304\einvoicevn.com\resources\report\60\95\ex_imp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\GENUWIN\19. Package\98. 2205 WABOOK\1.2307 WeTAX\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="18090" windowHeight="9990" tabRatio="754"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496" tabRatio="754"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="25" r:id="rId1"/>
@@ -632,16 +632,34 @@
     <t>(Chữ ký điện tử, chữ ký số)</t>
   </si>
   <si>
-    <t xml:space="preserve">MCCQT: </t>
-  </si>
-  <si>
     <t>Được ký bởi:</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">Thuế suất / </t>
+    </r>
     <r>
       <rPr>
         <i/>
         <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>VAT rate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: 0%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -651,7 +669,6 @@
     <r>
       <rPr>
         <b/>
-        <i/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
@@ -665,7 +682,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -851,6 +868,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1164,7 +1188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1185,14 +1209,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1318,6 +1338,144 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1339,203 +1497,78 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1817,205 +1850,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T48"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="2.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="1.7109375" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="1.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="1.6640625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="2.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="2.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="1.6640625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:18" s="9" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="78" t="s">
+    <row r="1" spans="1:20" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:20" s="9" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="83" t="s">
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="83"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="29"/>
-    </row>
-    <row r="3" spans="1:18" s="9" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="27"/>
+    </row>
+    <row r="3" spans="1:20" s="9" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="31"/>
-    </row>
-    <row r="4" spans="1:18" s="9" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="29"/>
+    </row>
+    <row r="4" spans="1:20" s="9" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="28"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="31"/>
-    </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="29"/>
+    </row>
+    <row r="5" spans="1:20" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="28"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="80" t="s">
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="80"/>
-      <c r="O5" s="88"/>
-      <c r="P5" s="88"/>
-      <c r="Q5" s="88"/>
-      <c r="R5" s="31"/>
-    </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="29"/>
+    </row>
+    <row r="6" spans="1:20" s="9" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="28"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="31"/>
-    </row>
-    <row r="7" spans="1:18" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="29"/>
+    </row>
+    <row r="7" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="30"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="89"/>
-      <c r="K7" s="89"/>
-      <c r="L7" s="89"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="33"/>
-    </row>
-    <row r="8" spans="1:18" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="114"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="114"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="116"/>
+      <c r="R7" s="116"/>
+      <c r="S7" s="116"/>
+      <c r="T7" s="31"/>
+    </row>
+    <row r="8" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="30"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="70"/>
-      <c r="R8" s="33"/>
-    </row>
-    <row r="9" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="34"/>
-    </row>
-    <row r="10" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126"/>
+      <c r="N8" s="126"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="31"/>
+    </row>
+    <row r="9" spans="1:20" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="32"/>
+    </row>
+    <row r="10" spans="1:20" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="30"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -2032,130 +2080,142 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
-      <c r="R10" s="34"/>
-    </row>
-    <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="32"/>
+    </row>
+    <row r="11" spans="1:20" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="30"/>
       <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="19" t="s">
+      <c r="C11" s="127"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="34"/>
-    </row>
-    <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="141"/>
+      <c r="P11" s="141"/>
+      <c r="Q11" s="141"/>
+      <c r="R11" s="141"/>
+      <c r="S11" s="141"/>
+      <c r="T11" s="32"/>
+    </row>
+    <row r="12" spans="1:20" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30"/>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="19" t="s">
+      <c r="C12" s="128"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="132"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="132"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="34"/>
-    </row>
-    <row r="13" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="144"/>
+      <c r="Q12" s="144"/>
+      <c r="R12" s="144"/>
+      <c r="S12" s="144"/>
+      <c r="T12" s="32"/>
+    </row>
+    <row r="13" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="30"/>
       <c r="B13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19" t="s">
+      <c r="C13" s="129"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="91"/>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="34"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="32"/>
-      <c r="B14" s="12" t="s">
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="139"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="139"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139"/>
+      <c r="T13" s="32"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="30"/>
+      <c r="B14" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="35"/>
-    </row>
-    <row r="15" spans="1:18" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="12" t="s">
+      <c r="G14" s="139"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="33"/>
+    </row>
+    <row r="15" spans="1:20" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="130"/>
-      <c r="R15" s="35"/>
-    </row>
-    <row r="16" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="111"/>
+      <c r="T15" s="33"/>
+    </row>
+    <row r="16" spans="1:20" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -2172,10 +2232,12 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="34"/>
-    </row>
-    <row r="17" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="32"/>
+    </row>
+    <row r="17" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34"/>
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
@@ -2183,21 +2245,23 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="37"/>
-    </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="36"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="115"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="115"/>
+      <c r="O17" s="115"/>
+      <c r="P17" s="115"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="115"/>
+      <c r="S17" s="115"/>
+      <c r="T17" s="35"/>
+    </row>
+    <row r="18" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34"/>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2205,31 +2269,33 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="37"/>
-    </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="36"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
+      <c r="T18" s="35"/>
+    </row>
+    <row r="19" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="139"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2238,100 +2304,110 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
-      <c r="R19" s="37"/>
-    </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="36"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="35"/>
+    </row>
+    <row r="20" spans="1:20" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34"/>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="37"/>
-    </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="36"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="118"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="118"/>
+      <c r="T20" s="35"/>
+    </row>
+    <row r="21" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34"/>
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="62"/>
-      <c r="R21" s="37"/>
-    </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="36"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="35"/>
+    </row>
+    <row r="22" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34"/>
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="37"/>
-    </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="36"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="35"/>
+    </row>
+    <row r="23" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34"/>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="F23" s="139"/>
+      <c r="G23" s="139"/>
+      <c r="H23" s="139"/>
+      <c r="I23" s="139"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="63" t="s">
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="37"/>
-    </row>
-    <row r="24" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="30"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2348,416 +2424,452 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
-      <c r="R24" s="34"/>
-    </row>
-    <row r="25" spans="1:18" s="50" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="46"/>
-      <c r="B25" s="47" t="s">
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="32"/>
+    </row>
+    <row r="25" spans="1:20" s="48" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="75" t="s">
+      <c r="C25" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="47" t="s">
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="120"/>
+      <c r="J25" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="61" t="s">
+      <c r="K25" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="75" t="s">
+      <c r="L25" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="76"/>
-      <c r="L25" s="47" t="s">
+      <c r="M25" s="120"/>
+      <c r="N25" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="M25" s="48" t="s">
+      <c r="O25" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="N25" s="48" t="s">
+      <c r="P25" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="O25" s="75" t="s">
+      <c r="Q25" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="P25" s="77"/>
-      <c r="Q25" s="76"/>
-      <c r="R25" s="49"/>
-    </row>
-    <row r="26" spans="1:18" s="54" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="51"/>
-      <c r="B26" s="52" t="s">
+      <c r="R25" s="121"/>
+      <c r="S25" s="120"/>
+      <c r="T25" s="47"/>
+    </row>
+    <row r="26" spans="1:20" s="52" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
+      <c r="B26" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="52" t="s">
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="52" t="s">
+      <c r="K26" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="95" t="s">
+      <c r="L26" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="96"/>
-      <c r="L26" s="52" t="s">
+      <c r="M26" s="106"/>
+      <c r="N26" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="M26" s="60" t="s">
+      <c r="O26" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="N26" s="60" t="s">
+      <c r="P26" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="O26" s="95" t="s">
+      <c r="Q26" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="P26" s="98"/>
-      <c r="Q26" s="96"/>
-      <c r="R26" s="53"/>
-    </row>
-    <row r="27" spans="1:18" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
+      <c r="R26" s="110"/>
+      <c r="S26" s="106"/>
+      <c r="T26" s="51"/>
+    </row>
+    <row r="27" spans="1:20" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
       <c r="B27" s="6">
         <v>1</v>
       </c>
-      <c r="C27" s="84">
+      <c r="C27" s="107">
         <v>2</v>
       </c>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="6">
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="6">
         <v>3</v>
       </c>
-      <c r="I27" s="6">
+      <c r="K27" s="6">
         <v>4</v>
       </c>
-      <c r="J27" s="84">
+      <c r="L27" s="107">
         <v>5</v>
       </c>
-      <c r="K27" s="85"/>
-      <c r="L27" s="6" t="s">
+      <c r="M27" s="109"/>
+      <c r="N27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M27" s="44">
+      <c r="O27" s="42">
         <v>7</v>
       </c>
-      <c r="N27" s="44">
+      <c r="P27" s="42">
         <v>8</v>
       </c>
-      <c r="O27" s="84" t="s">
+      <c r="Q27" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="85"/>
-      <c r="R27" s="66"/>
-    </row>
-    <row r="28" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="142"/>
-      <c r="O28" s="92"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="94"/>
-      <c r="R28" s="67"/>
-    </row>
-    <row r="29" spans="1:18" s="57" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="55"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="104" t="s">
+      <c r="R27" s="108"/>
+      <c r="S27" s="109"/>
+      <c r="T27" s="64"/>
+    </row>
+    <row r="28" spans="1:20" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="134"/>
+      <c r="N28" s="132"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="137"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="65"/>
+    </row>
+    <row r="29" spans="1:20" s="55" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I29" s="105"/>
-      <c r="J29" s="105"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="104" t="s">
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="M29" s="105"/>
-      <c r="N29" s="106"/>
-      <c r="O29" s="104" t="s">
+      <c r="O29" s="82"/>
+      <c r="P29" s="83"/>
+      <c r="Q29" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="68"/>
-    </row>
-    <row r="30" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="36"/>
-      <c r="B30" s="58" t="s">
+      <c r="R29" s="82"/>
+      <c r="S29" s="83"/>
+      <c r="T29" s="66"/>
+    </row>
+    <row r="30" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34"/>
+      <c r="B30" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="140"/>
-      <c r="J30" s="140"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="103"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="103"/>
-      <c r="R30" s="135"/>
-    </row>
-    <row r="31" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="36"/>
-      <c r="B31" s="58" t="s">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="77"/>
+      <c r="Q30" s="75"/>
+      <c r="R30" s="76"/>
+      <c r="S30" s="77"/>
+      <c r="T30" s="74"/>
+    </row>
+    <row r="31" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="78"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="80"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="76"/>
+      <c r="S31" s="77"/>
+      <c r="T31" s="74"/>
+    </row>
+    <row r="32" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="34"/>
+      <c r="B32" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="140"/>
-      <c r="J31" s="140"/>
-      <c r="K31" s="141"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="103"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="103"/>
-      <c r="R31" s="135"/>
-    </row>
-    <row r="32" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="36"/>
-      <c r="B32" s="58" t="s">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="80"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="77"/>
+      <c r="Q32" s="75"/>
+      <c r="R32" s="76"/>
+      <c r="S32" s="77"/>
+      <c r="T32" s="74"/>
+    </row>
+    <row r="33" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="34"/>
+      <c r="B33" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="140"/>
-      <c r="J32" s="140"/>
-      <c r="K32" s="141"/>
-      <c r="L32" s="101"/>
-      <c r="M32" s="102"/>
-      <c r="N32" s="103"/>
-      <c r="O32" s="101"/>
-      <c r="P32" s="102"/>
-      <c r="Q32" s="103"/>
-      <c r="R32" s="135"/>
-    </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="36"/>
-      <c r="B33" s="58" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="77"/>
+      <c r="Q33" s="75"/>
+      <c r="R33" s="76"/>
+      <c r="S33" s="77"/>
+      <c r="T33" s="74"/>
+    </row>
+    <row r="34" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="34"/>
+      <c r="B34" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="140"/>
-      <c r="J33" s="140"/>
-      <c r="K33" s="141"/>
-      <c r="L33" s="101"/>
-      <c r="M33" s="102"/>
-      <c r="N33" s="103"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="102"/>
-      <c r="Q33" s="103"/>
-      <c r="R33" s="135"/>
-    </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="36"/>
-      <c r="B34" s="58" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="77"/>
+      <c r="Q34" s="75"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="77"/>
+      <c r="T34" s="74"/>
+    </row>
+    <row r="35" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="34"/>
+      <c r="B35" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="140"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="141"/>
-      <c r="L34" s="101"/>
-      <c r="M34" s="102"/>
-      <c r="N34" s="103"/>
-      <c r="O34" s="101"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="103"/>
-      <c r="R34" s="135"/>
-    </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="36"/>
-      <c r="B35" s="59" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="78"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="77"/>
+      <c r="Q35" s="75"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="77"/>
+      <c r="T35" s="74"/>
+    </row>
+    <row r="36" spans="1:20" s="4" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="34"/>
+      <c r="B36" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="143"/>
-      <c r="I35" s="144"/>
-      <c r="J35" s="144"/>
-      <c r="K35" s="145"/>
-      <c r="L35" s="143"/>
-      <c r="M35" s="144"/>
-      <c r="N35" s="145"/>
-      <c r="O35" s="109"/>
-      <c r="P35" s="110"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="135"/>
-    </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="36"/>
-      <c r="B36" s="26" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="99"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
+      <c r="N36" s="99"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="101"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="104"/>
+      <c r="T36" s="74"/>
+    </row>
+    <row r="37" spans="1:20" s="4" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="107"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="107"/>
-      <c r="N36" s="107"/>
-      <c r="O36" s="107"/>
-      <c r="P36" s="107"/>
-      <c r="Q36" s="108"/>
-      <c r="R36" s="135"/>
-    </row>
-    <row r="37" spans="1:18" s="13" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="41"/>
-      <c r="B37" s="127" t="s">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="142"/>
+      <c r="K37" s="142"/>
+      <c r="L37" s="142"/>
+      <c r="M37" s="142"/>
+      <c r="N37" s="142"/>
+      <c r="O37" s="142"/>
+      <c r="P37" s="142"/>
+      <c r="Q37" s="142"/>
+      <c r="R37" s="142"/>
+      <c r="S37" s="143"/>
+      <c r="T37" s="74"/>
+    </row>
+    <row r="38" spans="1:20" s="12" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="39"/>
+      <c r="B38" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="127"/>
-      <c r="D37" s="127"/>
-      <c r="E37" s="127"/>
-      <c r="F37" s="127"/>
-      <c r="G37" s="127"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="127"/>
-      <c r="K37" s="127" t="s">
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="L37" s="127"/>
-      <c r="M37" s="127"/>
-      <c r="N37" s="127"/>
-      <c r="O37" s="127"/>
-      <c r="P37" s="127"/>
-      <c r="Q37" s="127"/>
-      <c r="R37" s="42"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="32"/>
-      <c r="B38" s="128" t="s">
+      <c r="N38" s="84"/>
+      <c r="O38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="84"/>
+      <c r="R38" s="84"/>
+      <c r="S38" s="84"/>
+      <c r="T38" s="40"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A39" s="30"/>
+      <c r="B39" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="128"/>
-      <c r="D38" s="128"/>
-      <c r="E38" s="128"/>
-      <c r="F38" s="128"/>
-      <c r="G38" s="129"/>
-      <c r="H38" s="129"/>
-      <c r="I38" s="129"/>
-      <c r="J38" s="129"/>
-      <c r="K38" s="129" t="s">
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="86"/>
+      <c r="K39" s="86"/>
+      <c r="L39" s="86"/>
+      <c r="M39" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="L38" s="129"/>
-      <c r="M38" s="129"/>
-      <c r="N38" s="129"/>
-      <c r="O38" s="129"/>
-      <c r="P38" s="129"/>
-      <c r="Q38" s="129"/>
-      <c r="R38" s="38"/>
-    </row>
-    <row r="39" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="32"/>
-      <c r="B39" s="82" t="s">
+      <c r="N39" s="86"/>
+      <c r="O39" s="86"/>
+      <c r="P39" s="86"/>
+      <c r="Q39" s="86"/>
+      <c r="R39" s="86"/>
+      <c r="S39" s="86"/>
+      <c r="T39" s="36"/>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="30"/>
+      <c r="B40" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="82"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="82" t="s">
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="L39" s="82"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="82"/>
-      <c r="O39" s="82"/>
-      <c r="P39" s="82"/>
-      <c r="Q39" s="82"/>
-      <c r="R39" s="35"/>
-    </row>
-    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="32"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="34"/>
-    </row>
-    <row r="41" spans="1:18" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="32"/>
+      <c r="N40" s="90"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="90"/>
+      <c r="S40" s="90"/>
+      <c r="T40" s="33"/>
+    </row>
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="30"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -2767,20 +2879,20 @@
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="115" t="s">
-        <v>10</v>
-      </c>
-      <c r="L41" s="116"/>
-      <c r="M41" s="116"/>
-      <c r="N41" s="116"/>
-      <c r="O41" s="116"/>
-      <c r="P41" s="116"/>
-      <c r="Q41" s="117"/>
-      <c r="R41" s="71"/>
-    </row>
-    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="32"/>
-      <c r="B42" s="23"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="32"/>
+    </row>
+    <row r="42" spans="1:20" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="30"/>
+      <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2789,63 +2901,71 @@
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="120" t="s">
-        <v>61</v>
-      </c>
-      <c r="L42" s="121"/>
-      <c r="M42" s="122"/>
-      <c r="N42" s="122"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="122"/>
-      <c r="Q42" s="123"/>
-      <c r="R42" s="71"/>
-    </row>
-    <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="32"/>
-      <c r="B43" s="24"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="N42" s="92"/>
+      <c r="O42" s="92"/>
+      <c r="P42" s="92"/>
+      <c r="Q42" s="92"/>
+      <c r="R42" s="92"/>
+      <c r="S42" s="93"/>
+      <c r="T42" s="69"/>
+    </row>
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="30"/>
+      <c r="B43" s="21"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="118"/>
-      <c r="G43" s="118"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="124" t="s">
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="N43" s="146"/>
+      <c r="O43" s="96"/>
+      <c r="P43" s="96"/>
+      <c r="Q43" s="96"/>
+      <c r="R43" s="96"/>
+      <c r="S43" s="97"/>
+      <c r="T43" s="69"/>
+    </row>
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="30"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="94"/>
+      <c r="J44" s="94"/>
+      <c r="K44" s="94"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="147" t="s">
         <v>62</v>
       </c>
-      <c r="L43" s="125"/>
-      <c r="M43" s="126"/>
-      <c r="N43" s="126"/>
-      <c r="O43" s="126"/>
-      <c r="P43" s="126"/>
-      <c r="Q43" s="72"/>
-      <c r="R43" s="34"/>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="32"/>
-      <c r="B44" s="69" t="s">
+      <c r="N44" s="148"/>
+      <c r="O44" s="98"/>
+      <c r="P44" s="98"/>
+      <c r="Q44" s="98"/>
+      <c r="R44" s="98"/>
+      <c r="S44" s="70"/>
+      <c r="T44" s="32"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A45" s="30"/>
+      <c r="B45" s="67" t="s">
         <v>53</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="119"/>
-      <c r="I44" s="119"/>
-      <c r="J44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="34"/>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="32"/>
-      <c r="B45" s="25" t="s">
-        <v>52</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -2853,134 +2973,167 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="24"/>
+      <c r="I45" s="95"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="95"/>
       <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="34"/>
-    </row>
-    <row r="46" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43"/>
-      <c r="B46" s="112" t="s">
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="8"/>
+      <c r="T45" s="32"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A46" s="30"/>
+      <c r="B46" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="32"/>
+    </row>
+    <row r="47" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="41"/>
+      <c r="B47" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="112"/>
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="112"/>
-      <c r="H46" s="112"/>
-      <c r="I46" s="112"/>
-      <c r="J46" s="112"/>
-      <c r="K46" s="112"/>
-      <c r="L46" s="112"/>
-      <c r="M46" s="112"/>
-      <c r="N46" s="112"/>
-      <c r="O46" s="112"/>
-      <c r="P46" s="112"/>
-      <c r="Q46" s="112"/>
-      <c r="R46" s="113"/>
-    </row>
-    <row r="47" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="114" t="s">
+      <c r="C47" s="87"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="87"/>
+      <c r="N47" s="87"/>
+      <c r="O47" s="87"/>
+      <c r="P47" s="87"/>
+      <c r="Q47" s="87"/>
+      <c r="R47" s="87"/>
+      <c r="S47" s="87"/>
+      <c r="T47" s="88"/>
+    </row>
+    <row r="48" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="114"/>
-      <c r="D47" s="114"/>
-      <c r="E47" s="114"/>
-      <c r="F47" s="114"/>
-      <c r="G47" s="114"/>
-      <c r="H47" s="114"/>
-      <c r="I47" s="114"/>
-      <c r="J47" s="114"/>
-      <c r="K47" s="114"/>
-      <c r="L47" s="114"/>
-      <c r="M47" s="114"/>
-      <c r="N47" s="114"/>
-      <c r="O47" s="114"/>
-      <c r="P47" s="114"/>
-      <c r="Q47" s="114"/>
-      <c r="R47" s="114"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="89"/>
+      <c r="J48" s="89"/>
+      <c r="K48" s="89"/>
+      <c r="L48" s="89"/>
+      <c r="M48" s="89"/>
+      <c r="N48" s="89"/>
+      <c r="O48" s="89"/>
+      <c r="P48" s="89"/>
+      <c r="Q48" s="89"/>
+      <c r="R48" s="89"/>
+      <c r="S48" s="89"/>
+      <c r="T48" s="89"/>
     </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="K37:Q37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="K38:Q38"/>
-    <mergeCell ref="B46:R46"/>
-    <mergeCell ref="B47:R47"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="K39:Q39"/>
-    <mergeCell ref="K41:Q41"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="M42:Q42"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="H36:Q36"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="F13:Q13"/>
-    <mergeCell ref="F11:Q11"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:Q15"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F12:Q12"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="F7:L7"/>
-    <mergeCell ref="G17:Q17"/>
-    <mergeCell ref="G18:Q18"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="D20:Q20"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="F2:L4"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F6:L6"/>
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="78">
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="D20:S20"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="H2:N4"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="H18:S18"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="B47:T47"/>
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="O44:R44"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\OneDrive\Máy tính\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AAD474-8C55-453A-93F1-95CC97250078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116C5C4A-68F9-415B-8183-7C4E72F4CC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="25" r:id="rId1"/>
@@ -893,7 +893,7 @@
     </font>
     <font>
       <i/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -913,7 +913,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1045,17 +1045,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -1211,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1253,33 +1242,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1288,25 +1277,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1336,23 +1325,23 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1376,29 +1365,173 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1410,179 +1543,41 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1865,32 +1860,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="1.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="2.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="2.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="1.7109375" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="1.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="1.7265625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="2.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7265625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7265625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="2.7265625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7265625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7265625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="1.7265625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:20" s="7" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:20" s="7" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1898,25 +1893,25 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="134" t="s">
+      <c r="H2" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="138" t="s">
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
-      <c r="S2" s="130"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
       <c r="T2" s="23"/>
     </row>
-    <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -1924,13 +1919,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="50"/>
       <c r="P3" s="50"/>
       <c r="Q3" s="57"/>
@@ -1938,7 +1933,7 @@
       <c r="S3" s="57"/>
       <c r="T3" s="25"/>
     </row>
-    <row r="4" spans="1:20" s="7" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" s="7" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1946,13 +1941,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="57"/>
@@ -1968,25 +1963,25 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="137" t="s">
+      <c r="H5" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="137"/>
-      <c r="J5" s="137"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="137"/>
-      <c r="M5" s="137"/>
-      <c r="N5" s="137"/>
-      <c r="O5" s="136" t="s">
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="136"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="121"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="98"/>
+      <c r="S5" s="98"/>
       <c r="T5" s="25"/>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1994,13 +1989,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="57"/>
@@ -2008,7 +2003,7 @@
       <c r="S6" s="57"/>
       <c r="T6" s="25"/>
     </row>
-    <row r="7" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2016,23 +2011,23 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="122" t="s">
+      <c r="H7" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="124"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="101"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="101"/>
       <c r="T7" s="27"/>
     </row>
-    <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2040,13 +2035,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="62"/>
@@ -2054,7 +2049,7 @@
       <c r="S8" s="62"/>
       <c r="T8" s="27"/>
     </row>
-    <row r="9" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -2076,11 +2071,11 @@
       <c r="S9" s="17"/>
       <c r="T9" s="28"/>
     </row>
-    <row r="10" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="26"/>
       <c r="T10" s="28"/>
     </row>
-    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="2" t="s">
         <v>40</v>
@@ -2091,22 +2086,22 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="125"/>
-      <c r="M11" s="125"/>
-      <c r="N11" s="125"/>
-      <c r="O11" s="125"/>
-      <c r="P11" s="125"/>
-      <c r="Q11" s="125"/>
-      <c r="R11" s="125"/>
-      <c r="S11" s="125"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+      <c r="N11" s="102"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="102"/>
+      <c r="Q11" s="102"/>
+      <c r="R11" s="102"/>
+      <c r="S11" s="102"/>
       <c r="T11" s="28"/>
     </row>
-    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="2" t="s">
         <v>41</v>
@@ -2117,22 +2112,22 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="126"/>
-      <c r="N12" s="126"/>
-      <c r="O12" s="126"/>
-      <c r="P12" s="126"/>
-      <c r="Q12" s="126"/>
-      <c r="R12" s="126"/>
-      <c r="S12" s="126"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
       <c r="T12" s="28"/>
     </row>
-    <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
@@ -2143,22 +2138,22 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="127"/>
-      <c r="P13" s="127"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="104"/>
       <c r="T13" s="28"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="26"/>
       <c r="B14" s="70" t="s">
         <v>43</v>
@@ -2167,10 +2162,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="128"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2182,7 +2177,7 @@
       <c r="S14" s="15"/>
       <c r="T14" s="28"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="70" t="s">
         <v>44</v>
@@ -2191,22 +2186,22 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
-      <c r="P15" s="120"/>
-      <c r="Q15" s="120"/>
-      <c r="R15" s="120"/>
-      <c r="S15" s="120"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="91"/>
+      <c r="S15" s="91"/>
       <c r="T15" s="28"/>
     </row>
-    <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2228,79 +2223,79 @@
       <c r="S16" s="3"/>
       <c r="T16" s="28"/>
     </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="123"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="123"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
       <c r="T17" s="30"/>
     </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="29"/>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="128"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="128"/>
-      <c r="L18" s="128"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="128"/>
-      <c r="O18" s="128"/>
-      <c r="P18" s="128"/>
-      <c r="Q18" s="128"/>
-      <c r="R18" s="128"/>
-      <c r="S18" s="128"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="89"/>
+      <c r="O18" s="89"/>
+      <c r="P18" s="89"/>
+      <c r="Q18" s="89"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="89"/>
       <c r="T18" s="30"/>
     </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29"/>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
       <c r="T19" s="30"/>
     </row>
-    <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29"/>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="129"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="129"/>
-      <c r="K20" s="129"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="129"/>
-      <c r="O20" s="129"/>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="129"/>
-      <c r="R20" s="129"/>
-      <c r="S20" s="129"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="79"/>
+      <c r="Q20" s="79"/>
+      <c r="R20" s="79"/>
+      <c r="S20" s="79"/>
       <c r="T20" s="30"/>
     </row>
-    <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
@@ -2310,9 +2305,9 @@
       <c r="F21" s="55"/>
       <c r="G21" s="55"/>
       <c r="H21" s="55"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
-      <c r="K21" s="129"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
       <c r="L21" s="55"/>
       <c r="M21" s="55"/>
       <c r="N21" s="55"/>
@@ -2323,7 +2318,7 @@
       <c r="S21" s="55"/>
       <c r="T21" s="30"/>
     </row>
-    <row r="22" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="29"/>
       <c r="B22" s="2" t="s">
         <v>49</v>
@@ -2334,9 +2329,9 @@
       <c r="G22" s="55"/>
       <c r="H22" s="55"/>
       <c r="I22" s="55"/>
-      <c r="J22" s="129"/>
-      <c r="K22" s="129"/>
-      <c r="L22" s="129"/>
+      <c r="J22" s="79"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
       <c r="M22" s="55"/>
       <c r="N22" s="55"/>
       <c r="O22" s="55"/>
@@ -2346,51 +2341,51 @@
       <c r="S22" s="55"/>
       <c r="T22" s="30"/>
     </row>
-    <row r="23" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="29"/>
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
       <c r="M23" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="122"/>
-      <c r="Q23" s="122"/>
-      <c r="R23" s="122"/>
+      <c r="P23" s="99"/>
+      <c r="Q23" s="99"/>
+      <c r="R23" s="99"/>
       <c r="T23" s="30"/>
     </row>
-    <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="T24" s="28"/>
     </row>
-    <row r="25" spans="1:20" s="43" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" s="43" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39"/>
       <c r="B25" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="131" t="s">
+      <c r="C25" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="133"/>
-      <c r="I25" s="132"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="81"/>
       <c r="J25" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K25" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="131" t="s">
+      <c r="L25" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="132"/>
+      <c r="M25" s="81"/>
       <c r="N25" s="40" t="s">
         <v>2</v>
       </c>
@@ -2400,37 +2395,37 @@
       <c r="P25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="131" t="s">
+      <c r="Q25" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="133"/>
-      <c r="S25" s="132"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="81"/>
       <c r="T25" s="42"/>
     </row>
-    <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
       <c r="B26" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="113" t="s">
+      <c r="C26" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="114"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="94"/>
       <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="113" t="s">
+      <c r="L26" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="114"/>
+      <c r="M26" s="94"/>
       <c r="N26" s="45" t="s">
         <v>9</v>
       </c>
@@ -2440,37 +2435,37 @@
       <c r="P26" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="113" t="s">
+      <c r="Q26" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="R26" s="118"/>
-      <c r="S26" s="114"/>
+      <c r="R26" s="93"/>
+      <c r="S26" s="94"/>
       <c r="T26" s="46"/>
     </row>
-    <row r="27" spans="1:20" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A27" s="32"/>
       <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="115">
+      <c r="C27" s="95">
         <v>2</v>
       </c>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="117"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="96"/>
       <c r="J27" s="4">
         <v>3</v>
       </c>
       <c r="K27" s="4">
         <v>4</v>
       </c>
-      <c r="L27" s="115">
+      <c r="L27" s="95">
         <v>5</v>
       </c>
-      <c r="M27" s="117"/>
+      <c r="M27" s="96"/>
       <c r="N27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2480,36 +2475,36 @@
       <c r="P27" s="37">
         <v>8</v>
       </c>
-      <c r="Q27" s="115" t="s">
+      <c r="Q27" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="116"/>
-      <c r="S27" s="117"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="96"/>
       <c r="T27" s="58"/>
     </row>
-    <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="71"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="112"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="109"/>
       <c r="N28" s="72"/>
       <c r="O28" s="73"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="110"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="112"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="142"/>
+      <c r="R28" s="143"/>
+      <c r="S28" s="144"/>
       <c r="T28" s="59"/>
     </row>
-    <row r="29" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="48"/>
       <c r="B29" s="49"/>
       <c r="C29" s="64"/>
@@ -2519,25 +2514,25 @@
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
       <c r="I29" s="65"/>
-      <c r="J29" s="107" t="s">
+      <c r="J29" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="109"/>
-      <c r="N29" s="107" t="s">
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="107"/>
+      <c r="N29" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="O29" s="108"/>
-      <c r="P29" s="109"/>
-      <c r="Q29" s="107" t="s">
+      <c r="O29" s="106"/>
+      <c r="P29" s="107"/>
+      <c r="Q29" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="R29" s="108"/>
-      <c r="S29" s="109"/>
+      <c r="R29" s="106"/>
+      <c r="S29" s="107"/>
       <c r="T29" s="60"/>
     </row>
-    <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
       <c r="B30" s="51" t="s">
         <v>53</v>
@@ -2549,19 +2544,19 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="94"/>
-      <c r="N30" s="95"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="97"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="96"/>
-      <c r="S30" s="97"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="115"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="116"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="113"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="112"/>
+      <c r="S30" s="113"/>
       <c r="T30" s="66"/>
     </row>
-    <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
       <c r="B31" s="51" t="s">
         <v>56</v>
@@ -2573,19 +2568,19 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="92"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="95"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="95"/>
-      <c r="R31" s="96"/>
-      <c r="S31" s="97"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="116"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="113"/>
       <c r="T31" s="66"/>
     </row>
-    <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29"/>
       <c r="B32" s="51" t="s">
         <v>52</v>
@@ -2597,19 +2592,19 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="95"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="95"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="97"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="115"/>
+      <c r="L32" s="115"/>
+      <c r="M32" s="116"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="113"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="112"/>
+      <c r="S32" s="113"/>
       <c r="T32" s="66"/>
     </row>
-    <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="51" t="s">
         <v>62</v>
@@ -2621,19 +2616,19 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="92"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="94"/>
-      <c r="N33" s="95"/>
-      <c r="O33" s="96"/>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="95"/>
-      <c r="R33" s="96"/>
-      <c r="S33" s="97"/>
+      <c r="J33" s="114"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="116"/>
+      <c r="N33" s="111"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="113"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="112"/>
+      <c r="S33" s="113"/>
       <c r="T33" s="66"/>
     </row>
-    <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29"/>
       <c r="B34" s="51" t="s">
         <v>61</v>
@@ -2645,19 +2640,19 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="96"/>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="95"/>
-      <c r="R34" s="96"/>
-      <c r="S34" s="97"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="115"/>
+      <c r="L34" s="115"/>
+      <c r="M34" s="116"/>
+      <c r="N34" s="111"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="113"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="112"/>
+      <c r="S34" s="113"/>
       <c r="T34" s="66"/>
     </row>
-    <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29"/>
       <c r="B35" s="51" t="s">
         <v>60</v>
@@ -2669,19 +2664,19 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="94"/>
-      <c r="N35" s="95"/>
-      <c r="O35" s="96"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="95"/>
-      <c r="R35" s="96"/>
-      <c r="S35" s="97"/>
+      <c r="J35" s="114"/>
+      <c r="K35" s="115"/>
+      <c r="L35" s="115"/>
+      <c r="M35" s="116"/>
+      <c r="N35" s="111"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="112"/>
+      <c r="S35" s="113"/>
       <c r="T35" s="66"/>
     </row>
-    <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29"/>
       <c r="B36" s="52" t="s">
         <v>27</v>
@@ -2693,19 +2688,19 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="98"/>
-      <c r="K36" s="99"/>
-      <c r="L36" s="99"/>
-      <c r="M36" s="100"/>
-      <c r="N36" s="98"/>
-      <c r="O36" s="99"/>
-      <c r="P36" s="100"/>
-      <c r="Q36" s="101"/>
-      <c r="R36" s="102"/>
-      <c r="S36" s="103"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="119"/>
+      <c r="O36" s="120"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="123"/>
+      <c r="S36" s="124"/>
       <c r="T36" s="66"/>
     </row>
-    <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29"/>
       <c r="B37" s="20" t="s">
         <v>48</v>
@@ -2716,121 +2711,121 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="104"/>
-      <c r="N37" s="104"/>
-      <c r="O37" s="104"/>
-      <c r="P37" s="104"/>
-      <c r="Q37" s="104"/>
-      <c r="R37" s="104"/>
-      <c r="S37" s="105"/>
+      <c r="I37" s="125"/>
+      <c r="J37" s="125"/>
+      <c r="K37" s="125"/>
+      <c r="L37" s="125"/>
+      <c r="M37" s="125"/>
+      <c r="N37" s="125"/>
+      <c r="O37" s="125"/>
+      <c r="P37" s="125"/>
+      <c r="Q37" s="125"/>
+      <c r="R37" s="125"/>
+      <c r="S37" s="126"/>
       <c r="T37" s="66"/>
     </row>
-    <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
-      <c r="B38" s="106" t="s">
+      <c r="B38" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="106"/>
-      <c r="D38" s="106"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="106"/>
-      <c r="H38" s="106"/>
-      <c r="I38" s="106"/>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="106" t="s">
+      <c r="C38" s="127"/>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="127"/>
+      <c r="J38" s="127"/>
+      <c r="K38" s="127"/>
+      <c r="L38" s="127"/>
+      <c r="M38" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="106"/>
-      <c r="O38" s="106"/>
-      <c r="P38" s="106"/>
-      <c r="Q38" s="106"/>
-      <c r="R38" s="106"/>
-      <c r="S38" s="106"/>
+      <c r="N38" s="127"/>
+      <c r="O38" s="127"/>
+      <c r="P38" s="127"/>
+      <c r="Q38" s="127"/>
+      <c r="R38" s="127"/>
+      <c r="S38" s="127"/>
       <c r="T38" s="35"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="90" t="s">
+      <c r="B39" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="91" t="s">
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
+      <c r="M39" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="91"/>
-      <c r="O39" s="91"/>
-      <c r="P39" s="91"/>
-      <c r="Q39" s="91"/>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91"/>
+      <c r="N39" s="118"/>
+      <c r="O39" s="118"/>
+      <c r="P39" s="118"/>
+      <c r="Q39" s="118"/>
+      <c r="R39" s="118"/>
+      <c r="S39" s="118"/>
       <c r="T39" s="31"/>
     </row>
-    <row r="40" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
-      <c r="M40" s="80" t="s">
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="87"/>
+      <c r="K40" s="87"/>
+      <c r="L40" s="87"/>
+      <c r="M40" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="N40" s="80"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80"/>
-      <c r="S40" s="80"/>
+      <c r="N40" s="87"/>
+      <c r="O40" s="87"/>
+      <c r="P40" s="87"/>
+      <c r="Q40" s="87"/>
+      <c r="R40" s="87"/>
+      <c r="S40" s="87"/>
       <c r="T40" s="28"/>
     </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="26"/>
       <c r="T41" s="28"/>
     </row>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="26"/>
-      <c r="M42" s="78" t="s">
+      <c r="M42" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N42" s="77"/>
-      <c r="O42" s="88"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="88"/>
-      <c r="R42" s="88"/>
-      <c r="S42" s="89"/>
+      <c r="N42" s="76"/>
+      <c r="O42" s="136"/>
+      <c r="P42" s="136"/>
+      <c r="Q42" s="136"/>
+      <c r="R42" s="136"/>
+      <c r="S42" s="137"/>
       <c r="T42" s="63"/>
     </row>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="18"/>
-      <c r="M43" s="82" t="s">
+      <c r="M43" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="83"/>
+      <c r="N43" s="131"/>
       <c r="O43" s="140"/>
       <c r="P43" s="140"/>
       <c r="Q43" s="140"/>
@@ -2838,108 +2833,173 @@
       <c r="S43" s="141"/>
       <c r="T43" s="63"/>
     </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="19"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="M44" s="84" t="s">
+      <c r="D44" s="129"/>
+      <c r="E44" s="129"/>
+      <c r="F44" s="129"/>
+      <c r="G44" s="129"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="129"/>
+      <c r="J44" s="129"/>
+      <c r="K44" s="129"/>
+      <c r="M44" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="85"/>
-      <c r="O44" s="142"/>
-      <c r="P44" s="142"/>
-      <c r="Q44" s="142"/>
-      <c r="R44" s="142"/>
-      <c r="S44" s="143"/>
+      <c r="N44" s="133"/>
+      <c r="O44" s="138"/>
+      <c r="P44" s="138"/>
+      <c r="Q44" s="138"/>
+      <c r="R44" s="138"/>
+      <c r="S44" s="139"/>
       <c r="T44" s="28"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="26"/>
       <c r="B45" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="87"/>
-      <c r="I45" s="87"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="87"/>
+      <c r="H45" s="135"/>
+      <c r="I45" s="135"/>
+      <c r="J45" s="135"/>
+      <c r="K45" s="135"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="28"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="26"/>
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="87"/>
-      <c r="J46" s="87"/>
-      <c r="K46" s="87"/>
-      <c r="L46" s="87"/>
-      <c r="M46" s="87"/>
-      <c r="N46" s="87"/>
-      <c r="O46" s="87"/>
-      <c r="P46" s="87"/>
-      <c r="Q46" s="87"/>
-      <c r="R46" s="87"/>
-      <c r="S46" s="87"/>
+      <c r="I46" s="135"/>
+      <c r="J46" s="135"/>
+      <c r="K46" s="135"/>
+      <c r="L46" s="135"/>
+      <c r="M46" s="135"/>
+      <c r="N46" s="135"/>
+      <c r="O46" s="135"/>
+      <c r="P46" s="135"/>
+      <c r="Q46" s="135"/>
+      <c r="R46" s="135"/>
+      <c r="S46" s="135"/>
       <c r="T46" s="28"/>
     </row>
-    <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="36"/>
-      <c r="B47" s="86" t="s">
+      <c r="B47" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="86"/>
-      <c r="D47" s="86"/>
-      <c r="E47" s="86"/>
-      <c r="F47" s="86"/>
-      <c r="G47" s="86"/>
-      <c r="H47" s="86"/>
-      <c r="I47" s="86"/>
-      <c r="J47" s="86"/>
-      <c r="K47" s="86"/>
-      <c r="L47" s="86"/>
-      <c r="M47" s="86"/>
-      <c r="N47" s="86"/>
-      <c r="O47" s="86"/>
-      <c r="P47" s="86"/>
-      <c r="Q47" s="86"/>
-      <c r="R47" s="86"/>
-      <c r="S47" s="86"/>
-      <c r="T47" s="75"/>
-    </row>
-    <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="79" t="s">
+      <c r="C47" s="134"/>
+      <c r="D47" s="134"/>
+      <c r="E47" s="134"/>
+      <c r="F47" s="134"/>
+      <c r="G47" s="134"/>
+      <c r="H47" s="134"/>
+      <c r="I47" s="134"/>
+      <c r="J47" s="134"/>
+      <c r="K47" s="134"/>
+      <c r="L47" s="134"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="134"/>
+      <c r="O47" s="134"/>
+      <c r="P47" s="134"/>
+      <c r="Q47" s="134"/>
+      <c r="R47" s="134"/>
+      <c r="S47" s="134"/>
+      <c r="T47" s="74"/>
+    </row>
+    <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="79"/>
-      <c r="G48" s="79"/>
-      <c r="H48" s="79"/>
-      <c r="I48" s="79"/>
-      <c r="J48" s="79"/>
-      <c r="K48" s="79"/>
-      <c r="L48" s="79"/>
-      <c r="M48" s="79"/>
-      <c r="N48" s="79"/>
-      <c r="O48" s="79"/>
-      <c r="P48" s="79"/>
-      <c r="Q48" s="79"/>
-      <c r="R48" s="79"/>
-      <c r="S48" s="79"/>
-      <c r="T48" s="79"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="128"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="128"/>
+      <c r="K48" s="128"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="128"/>
+      <c r="N48" s="128"/>
+      <c r="O48" s="128"/>
+      <c r="P48" s="128"/>
+      <c r="Q48" s="128"/>
+      <c r="R48" s="128"/>
+      <c r="S48" s="128"/>
+      <c r="T48" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="I46:S46"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="O44:S44"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I21:K21"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L25:M25"/>
@@ -2956,71 +3016,6 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="I37:S37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="B48:T48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:S40"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="I46:S46"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="O44:S44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116C5C4A-68F9-415B-8183-7C4E72F4CC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA836188-0628-4892-A2B6-A3DA9A5C7290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,7 +893,7 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1200,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1375,12 +1375,168 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1402,182 +1558,20 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1893,22 +1887,22 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="83" t="s">
+      <c r="H2" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="88" t="s">
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
+      <c r="P2" s="139"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="131"/>
       <c r="T2" s="23"/>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1919,13 +1913,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
       <c r="O3" s="50"/>
       <c r="P3" s="50"/>
       <c r="Q3" s="57"/>
@@ -1941,13 +1935,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="84"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="136"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="57"/>
@@ -1963,22 +1957,22 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="85" t="s">
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="138"/>
+      <c r="M5" s="138"/>
+      <c r="N5" s="138"/>
+      <c r="O5" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="98"/>
-      <c r="S5" s="98"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="122"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
       <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1989,13 +1983,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="87"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="57"/>
@@ -2011,20 +2005,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="99" t="s">
+      <c r="H7" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="101"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="125"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2035,13 +2029,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="62"/>
@@ -2086,19 +2080,19 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="126"/>
+      <c r="P11" s="126"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="126"/>
+      <c r="S11" s="126"/>
       <c r="T11" s="28"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2112,19 +2106,19 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
+      <c r="M12" s="127"/>
+      <c r="N12" s="127"/>
+      <c r="O12" s="127"/>
+      <c r="P12" s="127"/>
+      <c r="Q12" s="127"/>
+      <c r="R12" s="127"/>
+      <c r="S12" s="127"/>
       <c r="T12" s="28"/>
     </row>
     <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2138,19 +2132,19 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="104"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="128"/>
+      <c r="S13" s="128"/>
       <c r="T13" s="28"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2162,10 +2156,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2186,19 +2180,19 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="121"/>
+      <c r="S15" s="121"/>
       <c r="T15" s="28"/>
     </row>
     <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2228,17 +2222,17 @@
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="100"/>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="100"/>
-      <c r="S17" s="100"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="124"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="124"/>
+      <c r="N17" s="124"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
       <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2246,18 +2240,18 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="89"/>
-      <c r="O18" s="89"/>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="89"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="129"/>
+      <c r="M18" s="129"/>
+      <c r="N18" s="129"/>
+      <c r="O18" s="129"/>
+      <c r="P18" s="129"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="129"/>
+      <c r="S18" s="129"/>
       <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2265,11 +2259,11 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="129"/>
+      <c r="I19" s="129"/>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2277,22 +2271,22 @@
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="130"/>
+      <c r="L20" s="130"/>
+      <c r="M20" s="130"/>
+      <c r="N20" s="130"/>
+      <c r="O20" s="130"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="130"/>
+      <c r="R20" s="130"/>
+      <c r="S20" s="130"/>
       <c r="T20" s="30"/>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2305,9 +2299,9 @@
       <c r="F21" s="55"/>
       <c r="G21" s="55"/>
       <c r="H21" s="55"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="130"/>
+      <c r="K21" s="130"/>
       <c r="L21" s="55"/>
       <c r="M21" s="55"/>
       <c r="N21" s="55"/>
@@ -2329,9 +2323,9 @@
       <c r="G22" s="55"/>
       <c r="H22" s="55"/>
       <c r="I22" s="55"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
       <c r="M22" s="55"/>
       <c r="N22" s="55"/>
       <c r="O22" s="55"/>
@@ -2346,16 +2340,16 @@
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
       <c r="M23" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="99"/>
-      <c r="Q23" s="99"/>
-      <c r="R23" s="99"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="123"/>
       <c r="T23" s="30"/>
     </row>
     <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2367,25 +2361,25 @@
       <c r="B25" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="82"/>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="82"/>
-      <c r="I25" s="81"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="133"/>
       <c r="J25" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K25" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="80" t="s">
+      <c r="L25" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="81"/>
+      <c r="M25" s="133"/>
       <c r="N25" s="40" t="s">
         <v>2</v>
       </c>
@@ -2395,11 +2389,11 @@
       <c r="P25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="80" t="s">
+      <c r="Q25" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="82"/>
-      <c r="S25" s="81"/>
+      <c r="R25" s="134"/>
+      <c r="S25" s="133"/>
       <c r="T25" s="42"/>
     </row>
     <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2407,25 +2401,25 @@
       <c r="B26" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="94"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="113"/>
       <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="92" t="s">
+      <c r="L26" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="94"/>
+      <c r="M26" s="113"/>
       <c r="N26" s="45" t="s">
         <v>9</v>
       </c>
@@ -2435,11 +2429,11 @@
       <c r="P26" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="92" t="s">
+      <c r="Q26" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="R26" s="93"/>
-      <c r="S26" s="94"/>
+      <c r="R26" s="117"/>
+      <c r="S26" s="113"/>
       <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -2447,25 +2441,25 @@
       <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="95">
+      <c r="C27" s="114">
         <v>2</v>
       </c>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="96"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="116"/>
       <c r="J27" s="4">
         <v>3</v>
       </c>
       <c r="K27" s="4">
         <v>4</v>
       </c>
-      <c r="L27" s="95">
+      <c r="L27" s="114">
         <v>5</v>
       </c>
-      <c r="M27" s="96"/>
+      <c r="M27" s="116"/>
       <c r="N27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2475,33 +2469,33 @@
       <c r="P27" s="37">
         <v>8</v>
       </c>
-      <c r="Q27" s="95" t="s">
+      <c r="Q27" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="97"/>
-      <c r="S27" s="96"/>
+      <c r="R27" s="115"/>
+      <c r="S27" s="116"/>
       <c r="T27" s="58"/>
     </row>
     <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="71"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="109"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="119"/>
       <c r="N28" s="72"/>
       <c r="O28" s="73"/>
-      <c r="P28" s="145"/>
-      <c r="Q28" s="142"/>
-      <c r="R28" s="143"/>
-      <c r="S28" s="144"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="141"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="141"/>
       <c r="T28" s="59"/>
     </row>
     <row r="29" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2514,22 +2508,22 @@
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
       <c r="I29" s="65"/>
-      <c r="J29" s="105" t="s">
+      <c r="J29" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="107"/>
-      <c r="N29" s="105" t="s">
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
+      <c r="M29" s="111"/>
+      <c r="N29" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="O29" s="106"/>
-      <c r="P29" s="107"/>
-      <c r="Q29" s="105" t="s">
+      <c r="O29" s="110"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="R29" s="106"/>
-      <c r="S29" s="107"/>
+      <c r="R29" s="110"/>
+      <c r="S29" s="111"/>
       <c r="T29" s="60"/>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2544,16 +2538,16 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="115"/>
-      <c r="L30" s="115"/>
-      <c r="M30" s="116"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="113"/>
-      <c r="Q30" s="111"/>
-      <c r="R30" s="112"/>
-      <c r="S30" s="113"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="99"/>
+      <c r="Q30" s="97"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="99"/>
       <c r="T30" s="66"/>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2568,16 +2562,16 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="114"/>
-      <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="116"/>
-      <c r="N31" s="111"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="113"/>
-      <c r="Q31" s="111"/>
-      <c r="R31" s="112"/>
-      <c r="S31" s="113"/>
+      <c r="J31" s="94"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="97"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="99"/>
       <c r="T31" s="66"/>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2592,16 +2586,16 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="115"/>
-      <c r="M32" s="116"/>
-      <c r="N32" s="111"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="113"/>
-      <c r="Q32" s="111"/>
-      <c r="R32" s="112"/>
-      <c r="S32" s="113"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="99"/>
       <c r="T32" s="66"/>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2616,16 +2610,16 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="111"/>
-      <c r="O33" s="112"/>
-      <c r="P33" s="113"/>
-      <c r="Q33" s="111"/>
-      <c r="R33" s="112"/>
-      <c r="S33" s="113"/>
+      <c r="J33" s="94"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="98"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="97"/>
+      <c r="R33" s="98"/>
+      <c r="S33" s="99"/>
       <c r="T33" s="66"/>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2640,16 +2634,16 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="115"/>
-      <c r="L34" s="115"/>
-      <c r="M34" s="116"/>
-      <c r="N34" s="111"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="113"/>
-      <c r="Q34" s="111"/>
-      <c r="R34" s="112"/>
-      <c r="S34" s="113"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="98"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="97"/>
+      <c r="R34" s="98"/>
+      <c r="S34" s="99"/>
       <c r="T34" s="66"/>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2664,16 +2658,16 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="114"/>
-      <c r="K35" s="115"/>
-      <c r="L35" s="115"/>
-      <c r="M35" s="116"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="112"/>
-      <c r="P35" s="113"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="112"/>
-      <c r="S35" s="113"/>
+      <c r="J35" s="94"/>
+      <c r="K35" s="95"/>
+      <c r="L35" s="95"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="98"/>
+      <c r="P35" s="99"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
+      <c r="S35" s="99"/>
       <c r="T35" s="66"/>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2688,16 +2682,16 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="120"/>
-      <c r="L36" s="120"/>
-      <c r="M36" s="121"/>
-      <c r="N36" s="119"/>
-      <c r="O36" s="120"/>
-      <c r="P36" s="121"/>
-      <c r="Q36" s="122"/>
-      <c r="R36" s="123"/>
-      <c r="S36" s="124"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="101"/>
+      <c r="M36" s="102"/>
+      <c r="N36" s="100"/>
+      <c r="O36" s="101"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="103"/>
+      <c r="R36" s="104"/>
+      <c r="S36" s="105"/>
       <c r="T36" s="66"/>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2711,95 +2705,95 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="125"/>
-      <c r="J37" s="125"/>
-      <c r="K37" s="125"/>
-      <c r="L37" s="125"/>
-      <c r="M37" s="125"/>
-      <c r="N37" s="125"/>
-      <c r="O37" s="125"/>
-      <c r="P37" s="125"/>
-      <c r="Q37" s="125"/>
-      <c r="R37" s="125"/>
-      <c r="S37" s="126"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
+      <c r="S37" s="107"/>
       <c r="T37" s="66"/>
     </row>
     <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
-      <c r="B38" s="127" t="s">
+      <c r="B38" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="127"/>
-      <c r="D38" s="127"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="127"/>
-      <c r="H38" s="127"/>
-      <c r="I38" s="127"/>
-      <c r="J38" s="127"/>
-      <c r="K38" s="127"/>
-      <c r="L38" s="127"/>
-      <c r="M38" s="127" t="s">
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="127"/>
-      <c r="O38" s="127"/>
-      <c r="P38" s="127"/>
-      <c r="Q38" s="127"/>
-      <c r="R38" s="127"/>
-      <c r="S38" s="127"/>
+      <c r="N38" s="108"/>
+      <c r="O38" s="108"/>
+      <c r="P38" s="108"/>
+      <c r="Q38" s="108"/>
+      <c r="R38" s="108"/>
+      <c r="S38" s="108"/>
       <c r="T38" s="35"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="117" t="s">
+      <c r="B39" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="117"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="117"/>
-      <c r="H39" s="117"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="118"/>
-      <c r="K39" s="118"/>
-      <c r="L39" s="118"/>
-      <c r="M39" s="118" t="s">
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="118"/>
-      <c r="O39" s="118"/>
-      <c r="P39" s="118"/>
-      <c r="Q39" s="118"/>
-      <c r="R39" s="118"/>
-      <c r="S39" s="118"/>
+      <c r="N39" s="93"/>
+      <c r="O39" s="93"/>
+      <c r="P39" s="93"/>
+      <c r="Q39" s="93"/>
+      <c r="R39" s="93"/>
+      <c r="S39" s="93"/>
       <c r="T39" s="31"/>
     </row>
     <row r="40" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="87" t="s">
+      <c r="B40" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="87"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="87"/>
-      <c r="K40" s="87"/>
-      <c r="L40" s="87"/>
-      <c r="M40" s="87" t="s">
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="N40" s="87"/>
-      <c r="O40" s="87"/>
-      <c r="P40" s="87"/>
-      <c r="Q40" s="87"/>
-      <c r="R40" s="87"/>
-      <c r="S40" s="87"/>
+      <c r="N40" s="80"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80"/>
+      <c r="S40" s="80"/>
       <c r="T40" s="28"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2812,47 +2806,47 @@
         <v>10</v>
       </c>
       <c r="N42" s="76"/>
-      <c r="O42" s="136"/>
-      <c r="P42" s="136"/>
-      <c r="Q42" s="136"/>
-      <c r="R42" s="136"/>
-      <c r="S42" s="137"/>
+      <c r="O42" s="88"/>
+      <c r="P42" s="88"/>
+      <c r="Q42" s="88"/>
+      <c r="R42" s="88"/>
+      <c r="S42" s="89"/>
       <c r="T42" s="63"/>
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="18"/>
-      <c r="M43" s="130" t="s">
+      <c r="M43" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="131"/>
-      <c r="O43" s="140"/>
-      <c r="P43" s="140"/>
-      <c r="Q43" s="140"/>
-      <c r="R43" s="140"/>
-      <c r="S43" s="141"/>
+      <c r="N43" s="83"/>
+      <c r="O43" s="142"/>
+      <c r="P43" s="142"/>
+      <c r="Q43" s="142"/>
+      <c r="R43" s="142"/>
+      <c r="S43" s="143"/>
       <c r="T43" s="63"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="19"/>
-      <c r="D44" s="129"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="129"/>
-      <c r="I44" s="129"/>
-      <c r="J44" s="129"/>
-      <c r="K44" s="129"/>
-      <c r="M44" s="132" t="s">
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="M44" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="133"/>
-      <c r="O44" s="138"/>
-      <c r="P44" s="138"/>
-      <c r="Q44" s="138"/>
-      <c r="R44" s="138"/>
-      <c r="S44" s="139"/>
+      <c r="N44" s="85"/>
+      <c r="O44" s="90"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="90"/>
+      <c r="R44" s="90"/>
+      <c r="S44" s="91"/>
       <c r="T44" s="28"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
@@ -2860,10 +2854,10 @@
       <c r="B45" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="135"/>
-      <c r="I45" s="135"/>
-      <c r="J45" s="135"/>
-      <c r="K45" s="135"/>
+      <c r="H45" s="87"/>
+      <c r="I45" s="87"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="87"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="28"/>
@@ -2873,133 +2867,68 @@
       <c r="B46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="135"/>
-      <c r="J46" s="135"/>
-      <c r="K46" s="135"/>
-      <c r="L46" s="135"/>
-      <c r="M46" s="135"/>
-      <c r="N46" s="135"/>
-      <c r="O46" s="135"/>
-      <c r="P46" s="135"/>
-      <c r="Q46" s="135"/>
-      <c r="R46" s="135"/>
-      <c r="S46" s="135"/>
+      <c r="I46" s="87"/>
+      <c r="J46" s="87"/>
+      <c r="K46" s="87"/>
+      <c r="L46" s="87"/>
+      <c r="M46" s="87"/>
+      <c r="N46" s="87"/>
+      <c r="O46" s="87"/>
+      <c r="P46" s="87"/>
+      <c r="Q46" s="87"/>
+      <c r="R46" s="87"/>
+      <c r="S46" s="87"/>
       <c r="T46" s="28"/>
     </row>
     <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="36"/>
-      <c r="B47" s="134" t="s">
+      <c r="B47" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="134"/>
-      <c r="D47" s="134"/>
-      <c r="E47" s="134"/>
-      <c r="F47" s="134"/>
-      <c r="G47" s="134"/>
-      <c r="H47" s="134"/>
-      <c r="I47" s="134"/>
-      <c r="J47" s="134"/>
-      <c r="K47" s="134"/>
-      <c r="L47" s="134"/>
-      <c r="M47" s="134"/>
-      <c r="N47" s="134"/>
-      <c r="O47" s="134"/>
-      <c r="P47" s="134"/>
-      <c r="Q47" s="134"/>
-      <c r="R47" s="134"/>
-      <c r="S47" s="134"/>
+      <c r="C47" s="86"/>
+      <c r="D47" s="86"/>
+      <c r="E47" s="86"/>
+      <c r="F47" s="86"/>
+      <c r="G47" s="86"/>
+      <c r="H47" s="86"/>
+      <c r="I47" s="86"/>
+      <c r="J47" s="86"/>
+      <c r="K47" s="86"/>
+      <c r="L47" s="86"/>
+      <c r="M47" s="86"/>
+      <c r="N47" s="86"/>
+      <c r="O47" s="86"/>
+      <c r="P47" s="86"/>
+      <c r="Q47" s="86"/>
+      <c r="R47" s="86"/>
+      <c r="S47" s="86"/>
       <c r="T47" s="74"/>
     </row>
     <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="128" t="s">
+      <c r="B48" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="128"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="128"/>
-      <c r="F48" s="128"/>
-      <c r="G48" s="128"/>
-      <c r="H48" s="128"/>
-      <c r="I48" s="128"/>
-      <c r="J48" s="128"/>
-      <c r="K48" s="128"/>
-      <c r="L48" s="128"/>
-      <c r="M48" s="128"/>
-      <c r="N48" s="128"/>
-      <c r="O48" s="128"/>
-      <c r="P48" s="128"/>
-      <c r="Q48" s="128"/>
-      <c r="R48" s="128"/>
-      <c r="S48" s="128"/>
-      <c r="T48" s="128"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="79"/>
+      <c r="I48" s="79"/>
+      <c r="J48" s="79"/>
+      <c r="K48" s="79"/>
+      <c r="L48" s="79"/>
+      <c r="M48" s="79"/>
+      <c r="N48" s="79"/>
+      <c r="O48" s="79"/>
+      <c r="P48" s="79"/>
+      <c r="Q48" s="79"/>
+      <c r="R48" s="79"/>
+      <c r="S48" s="79"/>
+      <c r="T48" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="B48:T48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:S40"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="I46:S46"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="O44:S44"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="I37:S37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="I21:K21"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L25:M25"/>
@@ -3016,6 +2945,71 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="I46:S46"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="O44:S44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA836188-0628-4892-A2B6-A3DA9A5C7290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29F86C1-CA64-4771-B690-A97B3ECED1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1378,12 +1378,162 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1393,6 +1543,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1416,162 +1572,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1887,22 +1887,22 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="135" t="s">
+      <c r="H2" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="139" t="s">
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="139"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
       <c r="T2" s="23"/>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,13 +1913,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
       <c r="O3" s="50"/>
       <c r="P3" s="50"/>
       <c r="Q3" s="57"/>
@@ -1935,13 +1935,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="136"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="57"/>
@@ -1957,22 +1957,22 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="138" t="s">
+      <c r="H5" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="138"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="138"/>
-      <c r="L5" s="138"/>
-      <c r="M5" s="138"/>
-      <c r="N5" s="138"/>
-      <c r="O5" s="137" t="s">
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="122"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
       <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1983,13 +1983,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="57"/>
@@ -2005,20 +2005,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="123" t="s">
+      <c r="H7" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="137"/>
-      <c r="P7" s="137"/>
-      <c r="Q7" s="125"/>
-      <c r="R7" s="125"/>
-      <c r="S7" s="125"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
       <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2029,13 +2029,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="91"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="62"/>
@@ -2080,19 +2080,19 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="126"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="126"/>
-      <c r="P11" s="126"/>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="126"/>
-      <c r="S11" s="126"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="103"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
       <c r="T11" s="28"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2106,19 +2106,19 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
-      <c r="M12" s="127"/>
-      <c r="N12" s="127"/>
-      <c r="O12" s="127"/>
-      <c r="P12" s="127"/>
-      <c r="Q12" s="127"/>
-      <c r="R12" s="127"/>
-      <c r="S12" s="127"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="104"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="104"/>
+      <c r="Q12" s="104"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="104"/>
       <c r="T12" s="28"/>
     </row>
     <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2132,19 +2132,19 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="105"/>
+      <c r="R13" s="105"/>
+      <c r="S13" s="105"/>
       <c r="T13" s="28"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2156,10 +2156,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="129"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2180,19 +2180,19 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="121"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="121"/>
-      <c r="S15" s="121"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="92"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="92"/>
+      <c r="S15" s="92"/>
       <c r="T15" s="28"/>
     </row>
     <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2222,17 +2222,17 @@
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="101"/>
+      <c r="O17" s="101"/>
+      <c r="P17" s="101"/>
+      <c r="Q17" s="101"/>
+      <c r="R17" s="101"/>
+      <c r="S17" s="101"/>
       <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2240,18 +2240,18 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="129"/>
-      <c r="O18" s="129"/>
-      <c r="P18" s="129"/>
-      <c r="Q18" s="129"/>
-      <c r="R18" s="129"/>
-      <c r="S18" s="129"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
       <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2259,11 +2259,11 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2271,22 +2271,22 @@
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="130"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="130"/>
-      <c r="N20" s="130"/>
-      <c r="O20" s="130"/>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="130"/>
-      <c r="R20" s="130"/>
-      <c r="S20" s="130"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
       <c r="T20" s="30"/>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2299,9 +2299,9 @@
       <c r="F21" s="55"/>
       <c r="G21" s="55"/>
       <c r="H21" s="55"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="130"/>
-      <c r="K21" s="130"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
       <c r="L21" s="55"/>
       <c r="M21" s="55"/>
       <c r="N21" s="55"/>
@@ -2323,9 +2323,9 @@
       <c r="G22" s="55"/>
       <c r="H22" s="55"/>
       <c r="I22" s="55"/>
-      <c r="J22" s="130"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="130"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
       <c r="M22" s="55"/>
       <c r="N22" s="55"/>
       <c r="O22" s="55"/>
@@ -2340,16 +2340,16 @@
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="129"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
       <c r="M23" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="123"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="123"/>
+      <c r="P23" s="100"/>
+      <c r="Q23" s="100"/>
+      <c r="R23" s="100"/>
       <c r="T23" s="30"/>
     </row>
     <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2361,25 +2361,25 @@
       <c r="B25" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="132" t="s">
+      <c r="C25" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="134"/>
-      <c r="F25" s="134"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="133"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="82"/>
       <c r="J25" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K25" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="132" t="s">
+      <c r="L25" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="133"/>
+      <c r="M25" s="82"/>
       <c r="N25" s="40" t="s">
         <v>2</v>
       </c>
@@ -2389,11 +2389,11 @@
       <c r="P25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="132" t="s">
+      <c r="Q25" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="134"/>
-      <c r="S25" s="133"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="82"/>
       <c r="T25" s="42"/>
     </row>
     <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2401,25 +2401,25 @@
       <c r="B26" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="112" t="s">
+      <c r="C26" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="113"/>
+      <c r="D26" s="94"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="95"/>
       <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="112" t="s">
+      <c r="L26" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="113"/>
+      <c r="M26" s="95"/>
       <c r="N26" s="45" t="s">
         <v>9</v>
       </c>
@@ -2429,11 +2429,11 @@
       <c r="P26" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="112" t="s">
+      <c r="Q26" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="R26" s="117"/>
-      <c r="S26" s="113"/>
+      <c r="R26" s="94"/>
+      <c r="S26" s="95"/>
       <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -2441,25 +2441,25 @@
       <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="114">
+      <c r="C27" s="96">
         <v>2</v>
       </c>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="116"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="97"/>
       <c r="J27" s="4">
         <v>3</v>
       </c>
       <c r="K27" s="4">
         <v>4</v>
       </c>
-      <c r="L27" s="114">
+      <c r="L27" s="96">
         <v>5</v>
       </c>
-      <c r="M27" s="116"/>
+      <c r="M27" s="97"/>
       <c r="N27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2469,33 +2469,33 @@
       <c r="P27" s="37">
         <v>8</v>
       </c>
-      <c r="Q27" s="114" t="s">
+      <c r="Q27" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="115"/>
-      <c r="S27" s="116"/>
+      <c r="R27" s="98"/>
+      <c r="S27" s="97"/>
       <c r="T27" s="58"/>
     </row>
     <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="71"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="112"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="119"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="111"/>
       <c r="N28" s="72"/>
       <c r="O28" s="73"/>
       <c r="P28" s="78"/>
-      <c r="Q28" s="141"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="141"/>
+      <c r="Q28" s="109"/>
+      <c r="R28" s="109"/>
+      <c r="S28" s="109"/>
       <c r="T28" s="59"/>
     </row>
     <row r="29" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2508,22 +2508,22 @@
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
       <c r="I29" s="65"/>
-      <c r="J29" s="109" t="s">
+      <c r="J29" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="111"/>
-      <c r="N29" s="109" t="s">
+      <c r="K29" s="107"/>
+      <c r="L29" s="107"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="O29" s="110"/>
-      <c r="P29" s="111"/>
-      <c r="Q29" s="109" t="s">
+      <c r="O29" s="107"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="R29" s="110"/>
-      <c r="S29" s="111"/>
+      <c r="R29" s="107"/>
+      <c r="S29" s="108"/>
       <c r="T29" s="60"/>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2538,16 +2538,16 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="97"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="97"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="99"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="115"/>
+      <c r="Q30" s="113"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="115"/>
       <c r="T30" s="66"/>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2562,16 +2562,16 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="99"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="115"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="114"/>
+      <c r="S31" s="115"/>
       <c r="T31" s="66"/>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2586,16 +2586,16 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="95"/>
-      <c r="L32" s="95"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="97"/>
-      <c r="O32" s="98"/>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="97"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="99"/>
+      <c r="J32" s="116"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="118"/>
+      <c r="N32" s="113"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="115"/>
+      <c r="Q32" s="113"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="115"/>
       <c r="T32" s="66"/>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2610,16 +2610,16 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="95"/>
-      <c r="L33" s="95"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="98"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="97"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="99"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="118"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="114"/>
+      <c r="P33" s="115"/>
+      <c r="Q33" s="113"/>
+      <c r="R33" s="114"/>
+      <c r="S33" s="115"/>
       <c r="T33" s="66"/>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2634,16 +2634,16 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="95"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="98"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="98"/>
-      <c r="S34" s="99"/>
+      <c r="J34" s="116"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="117"/>
+      <c r="M34" s="118"/>
+      <c r="N34" s="113"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="115"/>
+      <c r="Q34" s="113"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="115"/>
       <c r="T34" s="66"/>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2658,16 +2658,16 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="95"/>
-      <c r="L35" s="95"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="98"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
-      <c r="S35" s="99"/>
+      <c r="J35" s="116"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+      <c r="M35" s="118"/>
+      <c r="N35" s="113"/>
+      <c r="O35" s="114"/>
+      <c r="P35" s="115"/>
+      <c r="Q35" s="113"/>
+      <c r="R35" s="114"/>
+      <c r="S35" s="115"/>
       <c r="T35" s="66"/>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2682,16 +2682,16 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="101"/>
-      <c r="L36" s="101"/>
-      <c r="M36" s="102"/>
-      <c r="N36" s="100"/>
-      <c r="O36" s="101"/>
-      <c r="P36" s="102"/>
-      <c r="Q36" s="103"/>
-      <c r="R36" s="104"/>
-      <c r="S36" s="105"/>
+      <c r="J36" s="121"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="123"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="123"/>
+      <c r="Q36" s="124"/>
+      <c r="R36" s="125"/>
+      <c r="S36" s="126"/>
       <c r="T36" s="66"/>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2705,95 +2705,95 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="106"/>
-      <c r="O37" s="106"/>
-      <c r="P37" s="106"/>
-      <c r="Q37" s="106"/>
-      <c r="R37" s="106"/>
-      <c r="S37" s="107"/>
+      <c r="I37" s="127"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="127"/>
+      <c r="N37" s="127"/>
+      <c r="O37" s="127"/>
+      <c r="P37" s="127"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="128"/>
       <c r="T37" s="66"/>
     </row>
     <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
-      <c r="B38" s="108" t="s">
+      <c r="B38" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="108"/>
-      <c r="K38" s="108"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="108" t="s">
+      <c r="C38" s="129"/>
+      <c r="D38" s="129"/>
+      <c r="E38" s="129"/>
+      <c r="F38" s="129"/>
+      <c r="G38" s="129"/>
+      <c r="H38" s="129"/>
+      <c r="I38" s="129"/>
+      <c r="J38" s="129"/>
+      <c r="K38" s="129"/>
+      <c r="L38" s="129"/>
+      <c r="M38" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="108"/>
-      <c r="O38" s="108"/>
-      <c r="P38" s="108"/>
-      <c r="Q38" s="108"/>
-      <c r="R38" s="108"/>
-      <c r="S38" s="108"/>
+      <c r="N38" s="129"/>
+      <c r="O38" s="129"/>
+      <c r="P38" s="129"/>
+      <c r="Q38" s="129"/>
+      <c r="R38" s="129"/>
+      <c r="S38" s="129"/>
       <c r="T38" s="35"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="92" t="s">
+      <c r="B39" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="92"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
-      <c r="H39" s="92"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93" t="s">
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119"/>
+      <c r="H39" s="119"/>
+      <c r="I39" s="120"/>
+      <c r="J39" s="120"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="120"/>
+      <c r="M39" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="93"/>
-      <c r="O39" s="93"/>
-      <c r="P39" s="93"/>
-      <c r="Q39" s="93"/>
-      <c r="R39" s="93"/>
-      <c r="S39" s="93"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="120"/>
+      <c r="P39" s="120"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="120"/>
+      <c r="S39" s="120"/>
       <c r="T39" s="31"/>
     </row>
     <row r="40" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
-      <c r="M40" s="80" t="s">
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="88"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
+      <c r="J40" s="88"/>
+      <c r="K40" s="88"/>
+      <c r="L40" s="88"/>
+      <c r="M40" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="N40" s="80"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80"/>
-      <c r="S40" s="80"/>
+      <c r="N40" s="88"/>
+      <c r="O40" s="88"/>
+      <c r="P40" s="88"/>
+      <c r="Q40" s="88"/>
+      <c r="R40" s="88"/>
+      <c r="S40" s="88"/>
       <c r="T40" s="28"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2806,47 +2806,47 @@
         <v>10</v>
       </c>
       <c r="N42" s="76"/>
-      <c r="O42" s="88"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="88"/>
-      <c r="R42" s="88"/>
-      <c r="S42" s="89"/>
+      <c r="O42" s="140"/>
+      <c r="P42" s="140"/>
+      <c r="Q42" s="140"/>
+      <c r="R42" s="140"/>
+      <c r="S42" s="141"/>
       <c r="T42" s="63"/>
     </row>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="18"/>
-      <c r="M43" s="82" t="s">
+      <c r="M43" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="83"/>
-      <c r="O43" s="142"/>
-      <c r="P43" s="142"/>
-      <c r="Q43" s="142"/>
-      <c r="R43" s="142"/>
-      <c r="S43" s="143"/>
+      <c r="N43" s="133"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="134"/>
+      <c r="Q43" s="134"/>
+      <c r="R43" s="134"/>
+      <c r="S43" s="135"/>
       <c r="T43" s="63"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="19"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="M44" s="84" t="s">
+      <c r="D44" s="131"/>
+      <c r="E44" s="131"/>
+      <c r="F44" s="131"/>
+      <c r="G44" s="131"/>
+      <c r="H44" s="131"/>
+      <c r="I44" s="131"/>
+      <c r="J44" s="131"/>
+      <c r="K44" s="131"/>
+      <c r="M44" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="85"/>
-      <c r="O44" s="90"/>
-      <c r="P44" s="90"/>
-      <c r="Q44" s="90"/>
-      <c r="R44" s="90"/>
-      <c r="S44" s="91"/>
+      <c r="N44" s="137"/>
+      <c r="O44" s="142"/>
+      <c r="P44" s="142"/>
+      <c r="Q44" s="142"/>
+      <c r="R44" s="142"/>
+      <c r="S44" s="143"/>
       <c r="T44" s="28"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
@@ -2854,10 +2854,10 @@
       <c r="B45" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="87"/>
-      <c r="I45" s="87"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="87"/>
+      <c r="H45" s="139"/>
+      <c r="I45" s="139"/>
+      <c r="J45" s="139"/>
+      <c r="K45" s="139"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="28"/>
@@ -2867,68 +2867,133 @@
       <c r="B46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="87"/>
-      <c r="J46" s="87"/>
-      <c r="K46" s="87"/>
-      <c r="L46" s="87"/>
-      <c r="M46" s="87"/>
-      <c r="N46" s="87"/>
-      <c r="O46" s="87"/>
-      <c r="P46" s="87"/>
-      <c r="Q46" s="87"/>
-      <c r="R46" s="87"/>
-      <c r="S46" s="87"/>
+      <c r="I46" s="139"/>
+      <c r="J46" s="139"/>
+      <c r="K46" s="139"/>
+      <c r="L46" s="139"/>
+      <c r="M46" s="139"/>
+      <c r="N46" s="139"/>
+      <c r="O46" s="139"/>
+      <c r="P46" s="139"/>
+      <c r="Q46" s="139"/>
+      <c r="R46" s="139"/>
+      <c r="S46" s="139"/>
       <c r="T46" s="28"/>
     </row>
     <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="36"/>
-      <c r="B47" s="86" t="s">
+      <c r="B47" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="86"/>
-      <c r="D47" s="86"/>
-      <c r="E47" s="86"/>
-      <c r="F47" s="86"/>
-      <c r="G47" s="86"/>
-      <c r="H47" s="86"/>
-      <c r="I47" s="86"/>
-      <c r="J47" s="86"/>
-      <c r="K47" s="86"/>
-      <c r="L47" s="86"/>
-      <c r="M47" s="86"/>
-      <c r="N47" s="86"/>
-      <c r="O47" s="86"/>
-      <c r="P47" s="86"/>
-      <c r="Q47" s="86"/>
-      <c r="R47" s="86"/>
-      <c r="S47" s="86"/>
+      <c r="C47" s="138"/>
+      <c r="D47" s="138"/>
+      <c r="E47" s="138"/>
+      <c r="F47" s="138"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="138"/>
+      <c r="I47" s="138"/>
+      <c r="J47" s="138"/>
+      <c r="K47" s="138"/>
+      <c r="L47" s="138"/>
+      <c r="M47" s="138"/>
+      <c r="N47" s="138"/>
+      <c r="O47" s="138"/>
+      <c r="P47" s="138"/>
+      <c r="Q47" s="138"/>
+      <c r="R47" s="138"/>
+      <c r="S47" s="138"/>
       <c r="T47" s="74"/>
     </row>
     <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="79" t="s">
+      <c r="B48" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="79"/>
-      <c r="G48" s="79"/>
-      <c r="H48" s="79"/>
-      <c r="I48" s="79"/>
-      <c r="J48" s="79"/>
-      <c r="K48" s="79"/>
-      <c r="L48" s="79"/>
-      <c r="M48" s="79"/>
-      <c r="N48" s="79"/>
-      <c r="O48" s="79"/>
-      <c r="P48" s="79"/>
-      <c r="Q48" s="79"/>
-      <c r="R48" s="79"/>
-      <c r="S48" s="79"/>
-      <c r="T48" s="79"/>
+      <c r="C48" s="130"/>
+      <c r="D48" s="130"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="130"/>
+      <c r="H48" s="130"/>
+      <c r="I48" s="130"/>
+      <c r="J48" s="130"/>
+      <c r="K48" s="130"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="130"/>
+      <c r="R48" s="130"/>
+      <c r="S48" s="130"/>
+      <c r="T48" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="I46:S46"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="O44:S44"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I21:K21"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L25:M25"/>
@@ -2945,71 +3010,6 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="I37:S37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="B48:T48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:S40"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="I46:S46"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="O44:S44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29F86C1-CA64-4771-B690-A97B3ECED1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92475CFC-3A1A-47D8-BFF7-5B25B6D3F649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25440" yWindow="3360" windowWidth="21600" windowHeight="11175" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="25" r:id="rId1"/>
@@ -1298,9 +1298,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1335,12 +1332,6 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1378,12 +1369,174 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1405,173 +1558,20 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1887,22 +1887,22 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="89" t="s">
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
+      <c r="P2" s="139"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="131"/>
       <c r="T2" s="23"/>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,18 +1913,18 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
       <c r="T3" s="25"/>
     </row>
     <row r="4" spans="1:20" s="7" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.3">
@@ -1935,18 +1935,18 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="136"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="57"/>
-      <c r="S4" s="57"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
       <c r="T4" s="25"/>
     </row>
     <row r="5" spans="1:20" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1957,22 +1957,22 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="87" t="s">
+      <c r="H5" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
-      <c r="N5" s="87"/>
-      <c r="O5" s="86" t="s">
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="138"/>
+      <c r="M5" s="138"/>
+      <c r="N5" s="138"/>
+      <c r="O5" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="122"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
       <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1983,18 +1983,18 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
       <c r="T6" s="25"/>
     </row>
     <row r="7" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2005,20 +2005,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="100" t="s">
+      <c r="H7" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="100"/>
-      <c r="N7" s="100"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="125"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2029,18 +2029,18 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="91"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="62"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="62"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="61"/>
       <c r="T8" s="27"/>
     </row>
     <row r="9" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2074,25 +2074,25 @@
       <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="67"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103"/>
-      <c r="L11" s="103"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="103"/>
-      <c r="S11" s="103"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="126"/>
+      <c r="P11" s="126"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="126"/>
+      <c r="S11" s="126"/>
       <c r="T11" s="28"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2100,25 +2100,25 @@
       <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="68"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="38"/>
       <c r="E12" s="38"/>
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="104"/>
-      <c r="P12" s="104"/>
-      <c r="Q12" s="104"/>
-      <c r="R12" s="104"/>
-      <c r="S12" s="104"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
+      <c r="M12" s="127"/>
+      <c r="N12" s="127"/>
+      <c r="O12" s="127"/>
+      <c r="P12" s="127"/>
+      <c r="Q12" s="127"/>
+      <c r="R12" s="127"/>
+      <c r="S12" s="127"/>
       <c r="T12" s="28"/>
     </row>
     <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2126,40 +2126,40 @@
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="69"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="105"/>
-      <c r="R13" s="105"/>
-      <c r="S13" s="105"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="128"/>
+      <c r="S13" s="128"/>
       <c r="T13" s="28"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="26"/>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="67" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2173,26 +2173,26 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="67" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="2"/>
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="92"/>
-      <c r="O15" s="92"/>
-      <c r="P15" s="92"/>
-      <c r="Q15" s="92"/>
-      <c r="R15" s="92"/>
-      <c r="S15" s="92"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="121"/>
+      <c r="S15" s="121"/>
       <c r="T15" s="28"/>
     </row>
     <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2222,17 +2222,17 @@
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="101"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="101"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="101"/>
-      <c r="N17" s="101"/>
-      <c r="O17" s="101"/>
-      <c r="P17" s="101"/>
-      <c r="Q17" s="101"/>
-      <c r="R17" s="101"/>
-      <c r="S17" s="101"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="124"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="124"/>
+      <c r="N17" s="124"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
       <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2240,18 +2240,18 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="90"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="90"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="90"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="129"/>
+      <c r="M18" s="129"/>
+      <c r="N18" s="129"/>
+      <c r="O18" s="129"/>
+      <c r="P18" s="129"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="129"/>
+      <c r="S18" s="129"/>
       <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2259,11 +2259,11 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="129"/>
+      <c r="I19" s="129"/>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2271,22 +2271,22 @@
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="80"/>
-      <c r="R20" s="80"/>
-      <c r="S20" s="80"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="130"/>
+      <c r="L20" s="130"/>
+      <c r="M20" s="130"/>
+      <c r="N20" s="130"/>
+      <c r="O20" s="130"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="130"/>
+      <c r="R20" s="130"/>
+      <c r="S20" s="130"/>
       <c r="T20" s="30"/>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2294,22 +2294,22 @@
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="130"/>
+      <c r="K21" s="130"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
       <c r="T21" s="30"/>
     </row>
     <row r="22" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2317,22 +2317,22 @@
       <c r="B22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
       <c r="T22" s="30"/>
     </row>
     <row r="23" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2340,16 +2340,16 @@
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="M23" s="56" t="s">
+      <c r="F23" s="129"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
+      <c r="M23" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="100"/>
-      <c r="Q23" s="100"/>
-      <c r="R23" s="100"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="123"/>
       <c r="T23" s="30"/>
     </row>
     <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2361,25 +2361,25 @@
       <c r="B25" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="82"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="133"/>
       <c r="J25" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="54" t="s">
+      <c r="K25" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="81" t="s">
+      <c r="L25" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="82"/>
+      <c r="M25" s="133"/>
       <c r="N25" s="40" t="s">
         <v>2</v>
       </c>
@@ -2389,11 +2389,11 @@
       <c r="P25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="81" t="s">
+      <c r="Q25" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="83"/>
-      <c r="S25" s="82"/>
+      <c r="R25" s="134"/>
+      <c r="S25" s="133"/>
       <c r="T25" s="42"/>
     </row>
     <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2401,39 +2401,39 @@
       <c r="B26" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="94"/>
-      <c r="E26" s="94"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="95"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="113"/>
       <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="93" t="s">
+      <c r="L26" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="95"/>
+      <c r="M26" s="113"/>
       <c r="N26" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="53" t="s">
+      <c r="O26" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="P26" s="53" t="s">
+      <c r="P26" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="93" t="s">
+      <c r="Q26" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="R26" s="94"/>
-      <c r="S26" s="95"/>
+      <c r="R26" s="117"/>
+      <c r="S26" s="113"/>
       <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -2441,25 +2441,25 @@
       <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="96">
+      <c r="C27" s="114">
         <v>2</v>
       </c>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="97"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="116"/>
       <c r="J27" s="4">
         <v>3</v>
       </c>
       <c r="K27" s="4">
         <v>4</v>
       </c>
-      <c r="L27" s="96">
+      <c r="L27" s="114">
         <v>5</v>
       </c>
-      <c r="M27" s="97"/>
+      <c r="M27" s="116"/>
       <c r="N27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2469,66 +2469,66 @@
       <c r="P27" s="37">
         <v>8</v>
       </c>
-      <c r="Q27" s="96" t="s">
+      <c r="Q27" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="98"/>
-      <c r="S27" s="97"/>
-      <c r="T27" s="58"/>
+      <c r="R27" s="115"/>
+      <c r="S27" s="116"/>
+      <c r="T27" s="57"/>
     </row>
     <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="112"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="109"/>
-      <c r="R28" s="109"/>
-      <c r="S28" s="109"/>
-      <c r="T28" s="59"/>
-    </row>
-    <row r="29" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="68"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="119"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="111"/>
+      <c r="S28" s="111"/>
+      <c r="T28" s="58"/>
+    </row>
+    <row r="29" spans="1:20" s="49" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="48"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="106" t="s">
+      <c r="B29" s="141"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="142"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="143"/>
+      <c r="J29" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="107"/>
-      <c r="L29" s="107"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="106" t="s">
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="O29" s="107"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="106" t="s">
+      <c r="O29" s="109"/>
+      <c r="P29" s="110"/>
+      <c r="Q29" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="R29" s="107"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="60"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="110"/>
+      <c r="T29" s="59"/>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>53</v>
       </c>
       <c r="C30" s="12"/>
@@ -2538,21 +2538,21 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="113"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="115"/>
-      <c r="Q30" s="113"/>
-      <c r="R30" s="114"/>
-      <c r="S30" s="115"/>
-      <c r="T30" s="66"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="94"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="96"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="98"/>
+      <c r="T30" s="63"/>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="50" t="s">
         <v>56</v>
       </c>
       <c r="C31" s="12"/>
@@ -2562,21 +2562,21 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="118"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="114"/>
-      <c r="P31" s="115"/>
-      <c r="Q31" s="113"/>
-      <c r="R31" s="114"/>
-      <c r="S31" s="115"/>
-      <c r="T31" s="66"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="94"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="98"/>
+      <c r="T31" s="63"/>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29"/>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="50" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="12"/>
@@ -2586,21 +2586,21 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="118"/>
-      <c r="N32" s="113"/>
-      <c r="O32" s="114"/>
-      <c r="P32" s="115"/>
-      <c r="Q32" s="113"/>
-      <c r="R32" s="114"/>
-      <c r="S32" s="115"/>
-      <c r="T32" s="66"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="94"/>
+      <c r="L32" s="94"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="63"/>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="50" t="s">
         <v>62</v>
       </c>
       <c r="C33" s="12"/>
@@ -2610,21 +2610,21 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="118"/>
-      <c r="N33" s="113"/>
-      <c r="O33" s="114"/>
-      <c r="P33" s="115"/>
-      <c r="Q33" s="113"/>
-      <c r="R33" s="114"/>
-      <c r="S33" s="115"/>
-      <c r="T33" s="66"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="94"/>
+      <c r="L33" s="94"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="96"/>
+      <c r="R33" s="97"/>
+      <c r="S33" s="98"/>
+      <c r="T33" s="63"/>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29"/>
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="50" t="s">
         <v>61</v>
       </c>
       <c r="C34" s="12"/>
@@ -2634,21 +2634,21 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="118"/>
-      <c r="N34" s="113"/>
-      <c r="O34" s="114"/>
-      <c r="P34" s="115"/>
-      <c r="Q34" s="113"/>
-      <c r="R34" s="114"/>
-      <c r="S34" s="115"/>
-      <c r="T34" s="66"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="94"/>
+      <c r="L34" s="94"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="97"/>
+      <c r="P34" s="98"/>
+      <c r="Q34" s="96"/>
+      <c r="R34" s="97"/>
+      <c r="S34" s="98"/>
+      <c r="T34" s="63"/>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29"/>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="50" t="s">
         <v>60</v>
       </c>
       <c r="C35" s="12"/>
@@ -2658,21 +2658,21 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="117"/>
-      <c r="M35" s="118"/>
-      <c r="N35" s="113"/>
-      <c r="O35" s="114"/>
-      <c r="P35" s="115"/>
-      <c r="Q35" s="113"/>
-      <c r="R35" s="114"/>
-      <c r="S35" s="115"/>
-      <c r="T35" s="66"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="94"/>
+      <c r="L35" s="94"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="98"/>
+      <c r="Q35" s="96"/>
+      <c r="R35" s="97"/>
+      <c r="S35" s="98"/>
+      <c r="T35" s="63"/>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29"/>
-      <c r="B36" s="52" t="s">
+      <c r="B36" s="51" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="12"/>
@@ -2682,17 +2682,17 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="121"/>
-      <c r="K36" s="122"/>
-      <c r="L36" s="122"/>
-      <c r="M36" s="123"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="122"/>
-      <c r="P36" s="123"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="125"/>
-      <c r="S36" s="126"/>
-      <c r="T36" s="66"/>
+      <c r="J36" s="99"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
+      <c r="N36" s="99"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="101"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="104"/>
+      <c r="T36" s="63"/>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29"/>
@@ -2705,95 +2705,95 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="127"/>
-      <c r="K37" s="127"/>
-      <c r="L37" s="127"/>
-      <c r="M37" s="127"/>
-      <c r="N37" s="127"/>
-      <c r="O37" s="127"/>
-      <c r="P37" s="127"/>
-      <c r="Q37" s="127"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="128"/>
-      <c r="T37" s="66"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="105"/>
+      <c r="N37" s="105"/>
+      <c r="O37" s="105"/>
+      <c r="P37" s="105"/>
+      <c r="Q37" s="105"/>
+      <c r="R37" s="105"/>
+      <c r="S37" s="106"/>
+      <c r="T37" s="63"/>
     </row>
     <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
-      <c r="B38" s="129" t="s">
+      <c r="B38" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="129"/>
-      <c r="D38" s="129"/>
-      <c r="E38" s="129"/>
-      <c r="F38" s="129"/>
-      <c r="G38" s="129"/>
-      <c r="H38" s="129"/>
-      <c r="I38" s="129"/>
-      <c r="J38" s="129"/>
-      <c r="K38" s="129"/>
-      <c r="L38" s="129"/>
-      <c r="M38" s="129" t="s">
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="129"/>
-      <c r="O38" s="129"/>
-      <c r="P38" s="129"/>
-      <c r="Q38" s="129"/>
-      <c r="R38" s="129"/>
-      <c r="S38" s="129"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
+      <c r="S38" s="107"/>
       <c r="T38" s="35"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="119" t="s">
+      <c r="B39" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="119"/>
-      <c r="H39" s="119"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="120"/>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120" t="s">
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="92"/>
+      <c r="L39" s="92"/>
+      <c r="M39" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
-      <c r="P39" s="120"/>
-      <c r="Q39" s="120"/>
-      <c r="R39" s="120"/>
-      <c r="S39" s="120"/>
+      <c r="N39" s="92"/>
+      <c r="O39" s="92"/>
+      <c r="P39" s="92"/>
+      <c r="Q39" s="92"/>
+      <c r="R39" s="92"/>
+      <c r="S39" s="92"/>
       <c r="T39" s="31"/>
     </row>
     <row r="40" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88"/>
-      <c r="H40" s="88"/>
-      <c r="I40" s="88"/>
-      <c r="J40" s="88"/>
-      <c r="K40" s="88"/>
-      <c r="L40" s="88"/>
-      <c r="M40" s="88" t="s">
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77"/>
+      <c r="M40" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="N40" s="88"/>
-      <c r="O40" s="88"/>
-      <c r="P40" s="88"/>
-      <c r="Q40" s="88"/>
-      <c r="R40" s="88"/>
-      <c r="S40" s="88"/>
+      <c r="N40" s="77"/>
+      <c r="O40" s="77"/>
+      <c r="P40" s="77"/>
+      <c r="Q40" s="77"/>
+      <c r="R40" s="77"/>
+      <c r="S40" s="77"/>
       <c r="T40" s="28"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2802,198 +2802,133 @@
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="26"/>
-      <c r="M42" s="77" t="s">
+      <c r="M42" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="N42" s="76"/>
-      <c r="O42" s="140"/>
-      <c r="P42" s="140"/>
-      <c r="Q42" s="140"/>
-      <c r="R42" s="140"/>
-      <c r="S42" s="141"/>
-      <c r="T42" s="63"/>
+      <c r="N42" s="73"/>
+      <c r="O42" s="87"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="87"/>
+      <c r="R42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="62"/>
     </row>
     <row r="43" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="18"/>
-      <c r="M43" s="132" t="s">
+      <c r="M43" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="133"/>
-      <c r="O43" s="134"/>
-      <c r="P43" s="134"/>
-      <c r="Q43" s="134"/>
-      <c r="R43" s="134"/>
-      <c r="S43" s="135"/>
-      <c r="T43" s="63"/>
+      <c r="N43" s="80"/>
+      <c r="O43" s="81"/>
+      <c r="P43" s="81"/>
+      <c r="Q43" s="81"/>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
+      <c r="T43" s="62"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="19"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="131"/>
-      <c r="F44" s="131"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="131"/>
-      <c r="J44" s="131"/>
-      <c r="K44" s="131"/>
-      <c r="M44" s="136" t="s">
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="M44" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="137"/>
-      <c r="O44" s="142"/>
-      <c r="P44" s="142"/>
-      <c r="Q44" s="142"/>
-      <c r="R44" s="142"/>
-      <c r="S44" s="143"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="89"/>
+      <c r="Q44" s="89"/>
+      <c r="R44" s="89"/>
+      <c r="S44" s="90"/>
       <c r="T44" s="28"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="26"/>
-      <c r="B45" s="61" t="s">
+      <c r="B45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="139"/>
-      <c r="K45" s="139"/>
+      <c r="H45" s="86"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+      <c r="K45" s="86"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="28"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="26"/>
-      <c r="B46" s="75" t="s">
+      <c r="B46" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="139"/>
-      <c r="J46" s="139"/>
-      <c r="K46" s="139"/>
-      <c r="L46" s="139"/>
-      <c r="M46" s="139"/>
-      <c r="N46" s="139"/>
-      <c r="O46" s="139"/>
-      <c r="P46" s="139"/>
-      <c r="Q46" s="139"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="139"/>
+      <c r="I46" s="86"/>
+      <c r="J46" s="86"/>
+      <c r="K46" s="86"/>
+      <c r="L46" s="86"/>
+      <c r="M46" s="86"/>
+      <c r="N46" s="86"/>
+      <c r="O46" s="86"/>
+      <c r="P46" s="86"/>
+      <c r="Q46" s="86"/>
+      <c r="R46" s="86"/>
+      <c r="S46" s="86"/>
       <c r="T46" s="28"/>
     </row>
     <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="36"/>
-      <c r="B47" s="138" t="s">
+      <c r="B47" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="138"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="138"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="138"/>
-      <c r="M47" s="138"/>
-      <c r="N47" s="138"/>
-      <c r="O47" s="138"/>
-      <c r="P47" s="138"/>
-      <c r="Q47" s="138"/>
-      <c r="R47" s="138"/>
-      <c r="S47" s="138"/>
-      <c r="T47" s="74"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
+      <c r="I47" s="85"/>
+      <c r="J47" s="85"/>
+      <c r="K47" s="85"/>
+      <c r="L47" s="85"/>
+      <c r="M47" s="85"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="85"/>
+      <c r="P47" s="85"/>
+      <c r="Q47" s="85"/>
+      <c r="R47" s="85"/>
+      <c r="S47" s="85"/>
+      <c r="T47" s="71"/>
     </row>
     <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="130" t="s">
+      <c r="B48" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="130"/>
-      <c r="D48" s="130"/>
-      <c r="E48" s="130"/>
-      <c r="F48" s="130"/>
-      <c r="G48" s="130"/>
-      <c r="H48" s="130"/>
-      <c r="I48" s="130"/>
-      <c r="J48" s="130"/>
-      <c r="K48" s="130"/>
-      <c r="L48" s="130"/>
-      <c r="M48" s="130"/>
-      <c r="N48" s="130"/>
-      <c r="O48" s="130"/>
-      <c r="P48" s="130"/>
-      <c r="Q48" s="130"/>
-      <c r="R48" s="130"/>
-      <c r="S48" s="130"/>
-      <c r="T48" s="130"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="76"/>
+      <c r="M48" s="76"/>
+      <c r="N48" s="76"/>
+      <c r="O48" s="76"/>
+      <c r="P48" s="76"/>
+      <c r="Q48" s="76"/>
+      <c r="R48" s="76"/>
+      <c r="S48" s="76"/>
+      <c r="T48" s="76"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="B48:T48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:S40"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="I46:S46"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="O44:S44"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="I37:S37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="I21:K21"/>
+  <mergeCells count="82">
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L25:M25"/>
@@ -3010,6 +2945,72 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="I46:S46"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="O44:S44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92475CFC-3A1A-47D8-BFF7-5B25B6D3F649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5409908-7D12-4252-890D-E50F76FB5B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25440" yWindow="3360" windowWidth="21600" windowHeight="11175" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="25" r:id="rId1"/>
@@ -1369,12 +1369,171 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1413,165 +1572,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1887,22 +1887,22 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="135" t="s">
+      <c r="H2" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="139" t="s">
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="139"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
       <c r="T2" s="23"/>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,13 +1913,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
       <c r="O3" s="49"/>
       <c r="P3" s="49"/>
       <c r="Q3" s="56"/>
@@ -1935,13 +1935,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="136"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="56"/>
@@ -1957,22 +1957,22 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="138" t="s">
+      <c r="H5" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="138"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="138"/>
-      <c r="L5" s="138"/>
-      <c r="M5" s="138"/>
-      <c r="N5" s="138"/>
-      <c r="O5" s="137" t="s">
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="122"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="96"/>
       <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1983,13 +1983,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
       <c r="O6" s="49"/>
       <c r="P6" s="49"/>
       <c r="Q6" s="56"/>
@@ -2005,20 +2005,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="123" t="s">
+      <c r="H7" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="137"/>
-      <c r="P7" s="137"/>
-      <c r="Q7" s="125"/>
-      <c r="R7" s="125"/>
-      <c r="S7" s="125"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
       <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2029,13 +2029,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="61"/>
@@ -2080,19 +2080,19 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="126"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="126"/>
-      <c r="P11" s="126"/>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="126"/>
-      <c r="S11" s="126"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
       <c r="T11" s="28"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2106,19 +2106,19 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
-      <c r="M12" s="127"/>
-      <c r="N12" s="127"/>
-      <c r="O12" s="127"/>
-      <c r="P12" s="127"/>
-      <c r="Q12" s="127"/>
-      <c r="R12" s="127"/>
-      <c r="S12" s="127"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="101"/>
       <c r="T12" s="28"/>
     </row>
     <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2132,19 +2132,19 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="102"/>
+      <c r="P13" s="102"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="102"/>
       <c r="T13" s="28"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2156,10 +2156,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="129"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2180,19 +2180,19 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="121"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="121"/>
-      <c r="S15" s="121"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
       <c r="T15" s="28"/>
     </row>
     <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2222,17 +2222,17 @@
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="98"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
       <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2240,18 +2240,18 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="129"/>
-      <c r="O18" s="129"/>
-      <c r="P18" s="129"/>
-      <c r="Q18" s="129"/>
-      <c r="R18" s="129"/>
-      <c r="S18" s="129"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
+      <c r="O18" s="87"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="87"/>
       <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2259,11 +2259,11 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2271,22 +2271,22 @@
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="130"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="130"/>
-      <c r="N20" s="130"/>
-      <c r="O20" s="130"/>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="130"/>
-      <c r="R20" s="130"/>
-      <c r="S20" s="130"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
+      <c r="Q20" s="77"/>
+      <c r="R20" s="77"/>
+      <c r="S20" s="77"/>
       <c r="T20" s="30"/>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2299,9 +2299,9 @@
       <c r="F21" s="54"/>
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="130"/>
-      <c r="K21" s="130"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
       <c r="L21" s="54"/>
       <c r="M21" s="54"/>
       <c r="N21" s="54"/>
@@ -2323,9 +2323,9 @@
       <c r="G22" s="54"/>
       <c r="H22" s="54"/>
       <c r="I22" s="54"/>
-      <c r="J22" s="130"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="130"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
       <c r="M22" s="54"/>
       <c r="N22" s="54"/>
       <c r="O22" s="54"/>
@@ -2340,16 +2340,16 @@
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="129"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="87"/>
       <c r="M23" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="123"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="123"/>
+      <c r="P23" s="97"/>
+      <c r="Q23" s="97"/>
+      <c r="R23" s="97"/>
       <c r="T23" s="30"/>
     </row>
     <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2361,25 +2361,25 @@
       <c r="B25" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="132" t="s">
+      <c r="C25" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="134"/>
-      <c r="F25" s="134"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="133"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="79"/>
       <c r="J25" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K25" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="132" t="s">
+      <c r="L25" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="133"/>
+      <c r="M25" s="79"/>
       <c r="N25" s="40" t="s">
         <v>2</v>
       </c>
@@ -2389,11 +2389,11 @@
       <c r="P25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="132" t="s">
+      <c r="Q25" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="134"/>
-      <c r="S25" s="133"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="79"/>
       <c r="T25" s="42"/>
     </row>
     <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2401,25 +2401,25 @@
       <c r="B26" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="112" t="s">
+      <c r="C26" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="113"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="91"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="92"/>
       <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="112" t="s">
+      <c r="L26" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="113"/>
+      <c r="M26" s="92"/>
       <c r="N26" s="45" t="s">
         <v>9</v>
       </c>
@@ -2429,11 +2429,11 @@
       <c r="P26" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="112" t="s">
+      <c r="Q26" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="R26" s="117"/>
-      <c r="S26" s="113"/>
+      <c r="R26" s="91"/>
+      <c r="S26" s="92"/>
       <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -2441,25 +2441,25 @@
       <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="114">
+      <c r="C27" s="93">
         <v>2</v>
       </c>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="116"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="94"/>
       <c r="J27" s="4">
         <v>3</v>
       </c>
       <c r="K27" s="4">
         <v>4</v>
       </c>
-      <c r="L27" s="114">
+      <c r="L27" s="93">
         <v>5</v>
       </c>
-      <c r="M27" s="116"/>
+      <c r="M27" s="94"/>
       <c r="N27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2469,61 +2469,61 @@
       <c r="P27" s="37">
         <v>8</v>
       </c>
-      <c r="Q27" s="114" t="s">
+      <c r="Q27" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="115"/>
-      <c r="S27" s="116"/>
+      <c r="R27" s="95"/>
+      <c r="S27" s="94"/>
       <c r="T27" s="57"/>
     </row>
     <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="68"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="109"/>
       <c r="J28" s="68"/>
       <c r="K28" s="69"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="119"/>
+      <c r="L28" s="107"/>
+      <c r="M28" s="108"/>
       <c r="N28" s="69"/>
       <c r="O28" s="70"/>
       <c r="P28" s="75"/>
-      <c r="Q28" s="111"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="111"/>
+      <c r="Q28" s="106"/>
+      <c r="R28" s="106"/>
+      <c r="S28" s="106"/>
       <c r="T28" s="58"/>
     </row>
     <row r="29" spans="1:20" s="49" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="48"/>
-      <c r="B29" s="141"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="143"/>
-      <c r="J29" s="108" t="s">
+      <c r="B29" s="110"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="109"/>
-      <c r="L29" s="109"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="108" t="s">
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="105"/>
+      <c r="N29" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="O29" s="109"/>
-      <c r="P29" s="110"/>
-      <c r="Q29" s="108" t="s">
+      <c r="O29" s="104"/>
+      <c r="P29" s="105"/>
+      <c r="Q29" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="R29" s="109"/>
-      <c r="S29" s="110"/>
+      <c r="R29" s="104"/>
+      <c r="S29" s="105"/>
       <c r="T29" s="59"/>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2538,16 +2538,16 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="94"/>
-      <c r="M30" s="95"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="97"/>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="96"/>
-      <c r="R30" s="97"/>
-      <c r="S30" s="98"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="115"/>
+      <c r="Q30" s="113"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="115"/>
       <c r="T30" s="63"/>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2562,16 +2562,16 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="94"/>
-      <c r="L31" s="94"/>
-      <c r="M31" s="95"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="96"/>
-      <c r="R31" s="97"/>
-      <c r="S31" s="98"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="115"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="114"/>
+      <c r="S31" s="115"/>
       <c r="T31" s="63"/>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2586,16 +2586,16 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="94"/>
-      <c r="L32" s="94"/>
-      <c r="M32" s="95"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="97"/>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="97"/>
-      <c r="S32" s="98"/>
+      <c r="J32" s="116"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="118"/>
+      <c r="N32" s="113"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="115"/>
+      <c r="Q32" s="113"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="115"/>
       <c r="T32" s="63"/>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2610,16 +2610,16 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="94"/>
-      <c r="L33" s="94"/>
-      <c r="M33" s="95"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="98"/>
-      <c r="Q33" s="96"/>
-      <c r="R33" s="97"/>
-      <c r="S33" s="98"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="118"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="114"/>
+      <c r="P33" s="115"/>
+      <c r="Q33" s="113"/>
+      <c r="R33" s="114"/>
+      <c r="S33" s="115"/>
       <c r="T33" s="63"/>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2634,16 +2634,16 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="95"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="96"/>
-      <c r="R34" s="97"/>
-      <c r="S34" s="98"/>
+      <c r="J34" s="116"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="117"/>
+      <c r="M34" s="118"/>
+      <c r="N34" s="113"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="115"/>
+      <c r="Q34" s="113"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="115"/>
       <c r="T34" s="63"/>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2658,16 +2658,16 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="94"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="95"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="98"/>
-      <c r="Q35" s="96"/>
-      <c r="R35" s="97"/>
-      <c r="S35" s="98"/>
+      <c r="J35" s="116"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+      <c r="M35" s="118"/>
+      <c r="N35" s="113"/>
+      <c r="O35" s="114"/>
+      <c r="P35" s="115"/>
+      <c r="Q35" s="113"/>
+      <c r="R35" s="114"/>
+      <c r="S35" s="115"/>
       <c r="T35" s="63"/>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2682,16 +2682,16 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="99"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="101"/>
-      <c r="N36" s="99"/>
-      <c r="O36" s="100"/>
-      <c r="P36" s="101"/>
-      <c r="Q36" s="102"/>
-      <c r="R36" s="103"/>
-      <c r="S36" s="104"/>
+      <c r="J36" s="121"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="123"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="123"/>
+      <c r="Q36" s="124"/>
+      <c r="R36" s="125"/>
+      <c r="S36" s="126"/>
       <c r="T36" s="63"/>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2705,95 +2705,95 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="105"/>
-      <c r="O37" s="105"/>
-      <c r="P37" s="105"/>
-      <c r="Q37" s="105"/>
-      <c r="R37" s="105"/>
-      <c r="S37" s="106"/>
+      <c r="I37" s="127"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="127"/>
+      <c r="N37" s="127"/>
+      <c r="O37" s="127"/>
+      <c r="P37" s="127"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="128"/>
       <c r="T37" s="63"/>
     </row>
     <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
-      <c r="E38" s="107"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="107"/>
-      <c r="H38" s="107"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="107"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="107"/>
-      <c r="M38" s="107" t="s">
+      <c r="C38" s="129"/>
+      <c r="D38" s="129"/>
+      <c r="E38" s="129"/>
+      <c r="F38" s="129"/>
+      <c r="G38" s="129"/>
+      <c r="H38" s="129"/>
+      <c r="I38" s="129"/>
+      <c r="J38" s="129"/>
+      <c r="K38" s="129"/>
+      <c r="L38" s="129"/>
+      <c r="M38" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="107"/>
-      <c r="O38" s="107"/>
-      <c r="P38" s="107"/>
-      <c r="Q38" s="107"/>
-      <c r="R38" s="107"/>
-      <c r="S38" s="107"/>
+      <c r="N38" s="129"/>
+      <c r="O38" s="129"/>
+      <c r="P38" s="129"/>
+      <c r="Q38" s="129"/>
+      <c r="R38" s="129"/>
+      <c r="S38" s="129"/>
       <c r="T38" s="35"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="91" t="s">
+      <c r="B39" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="92"/>
-      <c r="J39" s="92"/>
-      <c r="K39" s="92"/>
-      <c r="L39" s="92"/>
-      <c r="M39" s="92" t="s">
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119"/>
+      <c r="H39" s="119"/>
+      <c r="I39" s="120"/>
+      <c r="J39" s="120"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="120"/>
+      <c r="M39" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="92"/>
-      <c r="O39" s="92"/>
-      <c r="P39" s="92"/>
-      <c r="Q39" s="92"/>
-      <c r="R39" s="92"/>
-      <c r="S39" s="92"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="120"/>
+      <c r="P39" s="120"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="120"/>
+      <c r="S39" s="120"/>
       <c r="T39" s="31"/>
     </row>
     <row r="40" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77" t="s">
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="85"/>
+      <c r="G40" s="85"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="85"/>
+      <c r="M40" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="85"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
+      <c r="R40" s="85"/>
+      <c r="S40" s="85"/>
       <c r="T40" s="28"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2806,47 +2806,47 @@
         <v>10</v>
       </c>
       <c r="N42" s="73"/>
-      <c r="O42" s="87"/>
-      <c r="P42" s="87"/>
-      <c r="Q42" s="87"/>
-      <c r="R42" s="87"/>
-      <c r="S42" s="88"/>
+      <c r="O42" s="140"/>
+      <c r="P42" s="140"/>
+      <c r="Q42" s="140"/>
+      <c r="R42" s="140"/>
+      <c r="S42" s="141"/>
       <c r="T42" s="62"/>
     </row>
     <row r="43" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="18"/>
-      <c r="M43" s="79" t="s">
+      <c r="M43" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="80"/>
-      <c r="O43" s="81"/>
-      <c r="P43" s="81"/>
-      <c r="Q43" s="81"/>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="N43" s="133"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="134"/>
+      <c r="Q43" s="134"/>
+      <c r="R43" s="134"/>
+      <c r="S43" s="135"/>
       <c r="T43" s="62"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="19"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="M44" s="83" t="s">
+      <c r="D44" s="131"/>
+      <c r="E44" s="131"/>
+      <c r="F44" s="131"/>
+      <c r="G44" s="131"/>
+      <c r="H44" s="131"/>
+      <c r="I44" s="131"/>
+      <c r="J44" s="131"/>
+      <c r="K44" s="131"/>
+      <c r="M44" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="84"/>
-      <c r="O44" s="89"/>
-      <c r="P44" s="89"/>
-      <c r="Q44" s="89"/>
-      <c r="R44" s="89"/>
-      <c r="S44" s="90"/>
+      <c r="N44" s="137"/>
+      <c r="O44" s="142"/>
+      <c r="P44" s="142"/>
+      <c r="Q44" s="142"/>
+      <c r="R44" s="142"/>
+      <c r="S44" s="143"/>
       <c r="T44" s="28"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
@@ -2854,10 +2854,10 @@
       <c r="B45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="86"/>
-      <c r="I45" s="86"/>
-      <c r="J45" s="86"/>
-      <c r="K45" s="86"/>
+      <c r="H45" s="139"/>
+      <c r="I45" s="139"/>
+      <c r="J45" s="139"/>
+      <c r="K45" s="139"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="28"/>
@@ -2867,68 +2867,134 @@
       <c r="B46" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="86"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="86"/>
-      <c r="M46" s="86"/>
-      <c r="N46" s="86"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="86"/>
-      <c r="S46" s="86"/>
+      <c r="I46" s="139"/>
+      <c r="J46" s="139"/>
+      <c r="K46" s="139"/>
+      <c r="L46" s="139"/>
+      <c r="M46" s="139"/>
+      <c r="N46" s="139"/>
+      <c r="O46" s="139"/>
+      <c r="P46" s="139"/>
+      <c r="Q46" s="139"/>
+      <c r="R46" s="139"/>
+      <c r="S46" s="139"/>
       <c r="T46" s="28"/>
     </row>
     <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="36"/>
-      <c r="B47" s="85" t="s">
+      <c r="B47" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="85"/>
-      <c r="L47" s="85"/>
-      <c r="M47" s="85"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="85"/>
-      <c r="P47" s="85"/>
-      <c r="Q47" s="85"/>
-      <c r="R47" s="85"/>
-      <c r="S47" s="85"/>
+      <c r="C47" s="138"/>
+      <c r="D47" s="138"/>
+      <c r="E47" s="138"/>
+      <c r="F47" s="138"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="138"/>
+      <c r="I47" s="138"/>
+      <c r="J47" s="138"/>
+      <c r="K47" s="138"/>
+      <c r="L47" s="138"/>
+      <c r="M47" s="138"/>
+      <c r="N47" s="138"/>
+      <c r="O47" s="138"/>
+      <c r="P47" s="138"/>
+      <c r="Q47" s="138"/>
+      <c r="R47" s="138"/>
+      <c r="S47" s="138"/>
       <c r="T47" s="71"/>
     </row>
     <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="76" t="s">
+      <c r="B48" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="76"/>
-      <c r="K48" s="76"/>
-      <c r="L48" s="76"/>
-      <c r="M48" s="76"/>
-      <c r="N48" s="76"/>
-      <c r="O48" s="76"/>
-      <c r="P48" s="76"/>
-      <c r="Q48" s="76"/>
-      <c r="R48" s="76"/>
-      <c r="S48" s="76"/>
-      <c r="T48" s="76"/>
+      <c r="C48" s="130"/>
+      <c r="D48" s="130"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="130"/>
+      <c r="H48" s="130"/>
+      <c r="I48" s="130"/>
+      <c r="J48" s="130"/>
+      <c r="K48" s="130"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="130"/>
+      <c r="R48" s="130"/>
+      <c r="S48" s="130"/>
+      <c r="T48" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="I46:S46"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="O44:S44"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I21:K21"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L25:M25"/>
@@ -2945,72 +3011,6 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="I37:S37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="B48:T48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:S40"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="I46:S46"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="O44:S44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI_IMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5409908-7D12-4252-890D-E50F76FB5B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5CF42C-94A8-4284-93E2-0533908354D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1369,12 +1369,180 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1396,182 +1564,14 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1887,22 +1887,22 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="86" t="s">
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="133"/>
+      <c r="S2" s="133"/>
       <c r="T2" s="23"/>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,13 +1913,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
       <c r="O3" s="49"/>
       <c r="P3" s="49"/>
       <c r="Q3" s="56"/>
@@ -1935,13 +1935,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="56"/>
@@ -1957,22 +1957,22 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="84" t="s">
+      <c r="H5" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="83" t="s">
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
+      <c r="P5" s="139"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="124"/>
       <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1983,13 +1983,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
       <c r="O6" s="49"/>
       <c r="P6" s="49"/>
       <c r="Q6" s="56"/>
@@ -2005,20 +2005,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="97" t="s">
+      <c r="H7" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="139"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
+      <c r="S7" s="127"/>
       <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2029,13 +2029,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="88"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="142"/>
+      <c r="M8" s="142"/>
+      <c r="N8" s="142"/>
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="61"/>
@@ -2080,19 +2080,19 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="100"/>
-      <c r="N11" s="100"/>
-      <c r="O11" s="100"/>
-      <c r="P11" s="100"/>
-      <c r="Q11" s="100"/>
-      <c r="R11" s="100"/>
-      <c r="S11" s="100"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="128"/>
+      <c r="S11" s="128"/>
       <c r="T11" s="28"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2106,19 +2106,19 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="101"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+      <c r="M12" s="129"/>
+      <c r="N12" s="129"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="129"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="129"/>
+      <c r="S12" s="129"/>
       <c r="T12" s="28"/>
     </row>
     <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2132,19 +2132,19 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="102"/>
-      <c r="S13" s="102"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="130"/>
+      <c r="R13" s="130"/>
+      <c r="S13" s="130"/>
       <c r="T13" s="28"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2156,10 +2156,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2180,19 +2180,19 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="87"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="89"/>
-      <c r="O15" s="89"/>
-      <c r="P15" s="89"/>
-      <c r="Q15" s="89"/>
-      <c r="R15" s="89"/>
-      <c r="S15" s="89"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="123"/>
+      <c r="S15" s="123"/>
       <c r="T15" s="28"/>
     </row>
     <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2222,17 +2222,17 @@
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="98"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
       <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2240,18 +2240,18 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="87"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="87"/>
-      <c r="N18" s="87"/>
-      <c r="O18" s="87"/>
-      <c r="P18" s="87"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="87"/>
-      <c r="S18" s="87"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="131"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="131"/>
+      <c r="N18" s="131"/>
+      <c r="O18" s="131"/>
+      <c r="P18" s="131"/>
+      <c r="Q18" s="131"/>
+      <c r="R18" s="131"/>
+      <c r="S18" s="131"/>
       <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2259,11 +2259,11 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="131"/>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2271,22 +2271,22 @@
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="77"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="77"/>
-      <c r="P20" s="77"/>
-      <c r="Q20" s="77"/>
-      <c r="R20" s="77"/>
-      <c r="S20" s="77"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="132"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="132"/>
+      <c r="M20" s="132"/>
+      <c r="N20" s="132"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="132"/>
+      <c r="R20" s="132"/>
+      <c r="S20" s="132"/>
       <c r="T20" s="30"/>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2299,9 +2299,9 @@
       <c r="F21" s="54"/>
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132"/>
       <c r="L21" s="54"/>
       <c r="M21" s="54"/>
       <c r="N21" s="54"/>
@@ -2323,9 +2323,9 @@
       <c r="G22" s="54"/>
       <c r="H22" s="54"/>
       <c r="I22" s="54"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
       <c r="M22" s="54"/>
       <c r="N22" s="54"/>
       <c r="O22" s="54"/>
@@ -2340,16 +2340,16 @@
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="87"/>
-      <c r="G23" s="87"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="87"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="131"/>
       <c r="M23" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="97"/>
-      <c r="R23" s="97"/>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="125"/>
+      <c r="R23" s="125"/>
       <c r="T23" s="30"/>
     </row>
     <row r="24" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2361,25 +2361,25 @@
       <c r="B25" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="78" t="s">
+      <c r="C25" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="79"/>
+      <c r="D25" s="136"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="135"/>
       <c r="J25" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K25" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="78" t="s">
+      <c r="L25" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="79"/>
+      <c r="M25" s="135"/>
       <c r="N25" s="40" t="s">
         <v>2</v>
       </c>
@@ -2389,11 +2389,11 @@
       <c r="P25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="78" t="s">
+      <c r="Q25" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="80"/>
-      <c r="S25" s="79"/>
+      <c r="R25" s="136"/>
+      <c r="S25" s="135"/>
       <c r="T25" s="42"/>
     </row>
     <row r="26" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2401,25 +2401,25 @@
       <c r="B26" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="92"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="113"/>
       <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="90" t="s">
+      <c r="L26" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="92"/>
+      <c r="M26" s="113"/>
       <c r="N26" s="45" t="s">
         <v>9</v>
       </c>
@@ -2429,11 +2429,11 @@
       <c r="P26" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="90" t="s">
+      <c r="Q26" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="R26" s="91"/>
-      <c r="S26" s="92"/>
+      <c r="R26" s="117"/>
+      <c r="S26" s="113"/>
       <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -2441,25 +2441,25 @@
       <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="93">
+      <c r="C27" s="114">
         <v>2</v>
       </c>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="94"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="116"/>
       <c r="J27" s="4">
         <v>3</v>
       </c>
       <c r="K27" s="4">
         <v>4</v>
       </c>
-      <c r="L27" s="93">
+      <c r="L27" s="114">
         <v>5</v>
       </c>
-      <c r="M27" s="94"/>
+      <c r="M27" s="116"/>
       <c r="N27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2469,61 +2469,61 @@
       <c r="P27" s="37">
         <v>8</v>
       </c>
-      <c r="Q27" s="93" t="s">
+      <c r="Q27" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="95"/>
-      <c r="S27" s="94"/>
+      <c r="R27" s="115"/>
+      <c r="S27" s="116"/>
       <c r="T27" s="57"/>
     </row>
     <row r="28" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
       <c r="B28" s="68"/>
-      <c r="C28" s="109"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="109"/>
-      <c r="I28" s="109"/>
+      <c r="C28" s="143"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="143"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="143"/>
+      <c r="I28" s="143"/>
       <c r="J28" s="68"/>
       <c r="K28" s="69"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="108"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="119"/>
       <c r="N28" s="69"/>
       <c r="O28" s="70"/>
       <c r="P28" s="75"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="106"/>
-      <c r="S28" s="106"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="111"/>
+      <c r="S28" s="111"/>
       <c r="T28" s="58"/>
     </row>
     <row r="29" spans="1:20" s="49" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="48"/>
-      <c r="B29" s="110"/>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="112"/>
-      <c r="J29" s="103" t="s">
+      <c r="B29" s="120"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="122"/>
+      <c r="J29" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="105"/>
-      <c r="N29" s="103" t="s">
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="O29" s="104"/>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="103" t="s">
+      <c r="O29" s="109"/>
+      <c r="P29" s="110"/>
+      <c r="Q29" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="R29" s="104"/>
-      <c r="S29" s="105"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="110"/>
       <c r="T29" s="59"/>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2538,16 +2538,16 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="113"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="115"/>
-      <c r="Q30" s="113"/>
-      <c r="R30" s="114"/>
-      <c r="S30" s="115"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="94"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="96"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="98"/>
       <c r="T30" s="63"/>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2562,16 +2562,16 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="118"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="114"/>
-      <c r="P31" s="115"/>
-      <c r="Q31" s="113"/>
-      <c r="R31" s="114"/>
-      <c r="S31" s="115"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="94"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="98"/>
       <c r="T31" s="63"/>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2586,16 +2586,16 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="118"/>
-      <c r="N32" s="113"/>
-      <c r="O32" s="114"/>
-      <c r="P32" s="115"/>
-      <c r="Q32" s="113"/>
-      <c r="R32" s="114"/>
-      <c r="S32" s="115"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="94"/>
+      <c r="L32" s="94"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="98"/>
       <c r="T32" s="63"/>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2610,16 +2610,16 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="118"/>
-      <c r="N33" s="113"/>
-      <c r="O33" s="114"/>
-      <c r="P33" s="115"/>
-      <c r="Q33" s="113"/>
-      <c r="R33" s="114"/>
-      <c r="S33" s="115"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="94"/>
+      <c r="L33" s="94"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="96"/>
+      <c r="R33" s="97"/>
+      <c r="S33" s="98"/>
       <c r="T33" s="63"/>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2634,16 +2634,16 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="118"/>
-      <c r="N34" s="113"/>
-      <c r="O34" s="114"/>
-      <c r="P34" s="115"/>
-      <c r="Q34" s="113"/>
-      <c r="R34" s="114"/>
-      <c r="S34" s="115"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="94"/>
+      <c r="L34" s="94"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="97"/>
+      <c r="P34" s="98"/>
+      <c r="Q34" s="96"/>
+      <c r="R34" s="97"/>
+      <c r="S34" s="98"/>
       <c r="T34" s="63"/>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2658,16 +2658,16 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="117"/>
-      <c r="M35" s="118"/>
-      <c r="N35" s="113"/>
-      <c r="O35" s="114"/>
-      <c r="P35" s="115"/>
-      <c r="Q35" s="113"/>
-      <c r="R35" s="114"/>
-      <c r="S35" s="115"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="94"/>
+      <c r="L35" s="94"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="98"/>
+      <c r="Q35" s="96"/>
+      <c r="R35" s="97"/>
+      <c r="S35" s="98"/>
       <c r="T35" s="63"/>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2682,16 +2682,16 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="121"/>
-      <c r="K36" s="122"/>
-      <c r="L36" s="122"/>
-      <c r="M36" s="123"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="122"/>
-      <c r="P36" s="123"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="125"/>
-      <c r="S36" s="126"/>
+      <c r="J36" s="99"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
+      <c r="N36" s="99"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="101"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="104"/>
       <c r="T36" s="63"/>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2705,95 +2705,95 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="127"/>
-      <c r="K37" s="127"/>
-      <c r="L37" s="127"/>
-      <c r="M37" s="127"/>
-      <c r="N37" s="127"/>
-      <c r="O37" s="127"/>
-      <c r="P37" s="127"/>
-      <c r="Q37" s="127"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="128"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="105"/>
+      <c r="N37" s="105"/>
+      <c r="O37" s="105"/>
+      <c r="P37" s="105"/>
+      <c r="Q37" s="105"/>
+      <c r="R37" s="105"/>
+      <c r="S37" s="106"/>
       <c r="T37" s="63"/>
     </row>
     <row r="38" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
-      <c r="B38" s="129" t="s">
+      <c r="B38" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="129"/>
-      <c r="D38" s="129"/>
-      <c r="E38" s="129"/>
-      <c r="F38" s="129"/>
-      <c r="G38" s="129"/>
-      <c r="H38" s="129"/>
-      <c r="I38" s="129"/>
-      <c r="J38" s="129"/>
-      <c r="K38" s="129"/>
-      <c r="L38" s="129"/>
-      <c r="M38" s="129" t="s">
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="129"/>
-      <c r="O38" s="129"/>
-      <c r="P38" s="129"/>
-      <c r="Q38" s="129"/>
-      <c r="R38" s="129"/>
-      <c r="S38" s="129"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
+      <c r="S38" s="107"/>
       <c r="T38" s="35"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="119" t="s">
+      <c r="B39" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="119"/>
-      <c r="H39" s="119"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="120"/>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120" t="s">
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="92"/>
+      <c r="L39" s="92"/>
+      <c r="M39" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
-      <c r="P39" s="120"/>
-      <c r="Q39" s="120"/>
-      <c r="R39" s="120"/>
-      <c r="S39" s="120"/>
+      <c r="N39" s="92"/>
+      <c r="O39" s="92"/>
+      <c r="P39" s="92"/>
+      <c r="Q39" s="92"/>
+      <c r="R39" s="92"/>
+      <c r="S39" s="92"/>
       <c r="T39" s="31"/>
     </row>
     <row r="40" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="85" t="s">
+      <c r="B40" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85"/>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="85"/>
-      <c r="M40" s="85" t="s">
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77"/>
+      <c r="M40" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="N40" s="85"/>
-      <c r="O40" s="85"/>
-      <c r="P40" s="85"/>
-      <c r="Q40" s="85"/>
-      <c r="R40" s="85"/>
-      <c r="S40" s="85"/>
+      <c r="N40" s="77"/>
+      <c r="O40" s="77"/>
+      <c r="P40" s="77"/>
+      <c r="Q40" s="77"/>
+      <c r="R40" s="77"/>
+      <c r="S40" s="77"/>
       <c r="T40" s="28"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2806,47 +2806,47 @@
         <v>10</v>
       </c>
       <c r="N42" s="73"/>
-      <c r="O42" s="140"/>
-      <c r="P42" s="140"/>
-      <c r="Q42" s="140"/>
-      <c r="R42" s="140"/>
-      <c r="S42" s="141"/>
+      <c r="O42" s="87"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="87"/>
+      <c r="R42" s="87"/>
+      <c r="S42" s="88"/>
       <c r="T42" s="62"/>
     </row>
     <row r="43" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="18"/>
-      <c r="M43" s="132" t="s">
+      <c r="M43" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="133"/>
-      <c r="O43" s="134"/>
-      <c r="P43" s="134"/>
-      <c r="Q43" s="134"/>
-      <c r="R43" s="134"/>
-      <c r="S43" s="135"/>
+      <c r="N43" s="80"/>
+      <c r="O43" s="81"/>
+      <c r="P43" s="81"/>
+      <c r="Q43" s="81"/>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
       <c r="T43" s="62"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="19"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="131"/>
-      <c r="F44" s="131"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="131"/>
-      <c r="J44" s="131"/>
-      <c r="K44" s="131"/>
-      <c r="M44" s="136" t="s">
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="M44" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="137"/>
-      <c r="O44" s="142"/>
-      <c r="P44" s="142"/>
-      <c r="Q44" s="142"/>
-      <c r="R44" s="142"/>
-      <c r="S44" s="143"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="89"/>
+      <c r="Q44" s="89"/>
+      <c r="R44" s="89"/>
+      <c r="S44" s="90"/>
       <c r="T44" s="28"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
@@ -2854,10 +2854,10 @@
       <c r="B45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="139"/>
-      <c r="K45" s="139"/>
+      <c r="H45" s="86"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+      <c r="K45" s="86"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="28"/>
@@ -2867,134 +2867,68 @@
       <c r="B46" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="139"/>
-      <c r="J46" s="139"/>
-      <c r="K46" s="139"/>
-      <c r="L46" s="139"/>
-      <c r="M46" s="139"/>
-      <c r="N46" s="139"/>
-      <c r="O46" s="139"/>
-      <c r="P46" s="139"/>
-      <c r="Q46" s="139"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="139"/>
+      <c r="I46" s="86"/>
+      <c r="J46" s="86"/>
+      <c r="K46" s="86"/>
+      <c r="L46" s="86"/>
+      <c r="M46" s="86"/>
+      <c r="N46" s="86"/>
+      <c r="O46" s="86"/>
+      <c r="P46" s="86"/>
+      <c r="Q46" s="86"/>
+      <c r="R46" s="86"/>
+      <c r="S46" s="86"/>
       <c r="T46" s="28"/>
     </row>
     <row r="47" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="36"/>
-      <c r="B47" s="138" t="s">
+      <c r="B47" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="138"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="138"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="138"/>
-      <c r="M47" s="138"/>
-      <c r="N47" s="138"/>
-      <c r="O47" s="138"/>
-      <c r="P47" s="138"/>
-      <c r="Q47" s="138"/>
-      <c r="R47" s="138"/>
-      <c r="S47" s="138"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
+      <c r="I47" s="85"/>
+      <c r="J47" s="85"/>
+      <c r="K47" s="85"/>
+      <c r="L47" s="85"/>
+      <c r="M47" s="85"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="85"/>
+      <c r="P47" s="85"/>
+      <c r="Q47" s="85"/>
+      <c r="R47" s="85"/>
+      <c r="S47" s="85"/>
       <c r="T47" s="71"/>
     </row>
     <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="130" t="s">
+      <c r="B48" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="130"/>
-      <c r="D48" s="130"/>
-      <c r="E48" s="130"/>
-      <c r="F48" s="130"/>
-      <c r="G48" s="130"/>
-      <c r="H48" s="130"/>
-      <c r="I48" s="130"/>
-      <c r="J48" s="130"/>
-      <c r="K48" s="130"/>
-      <c r="L48" s="130"/>
-      <c r="M48" s="130"/>
-      <c r="N48" s="130"/>
-      <c r="O48" s="130"/>
-      <c r="P48" s="130"/>
-      <c r="Q48" s="130"/>
-      <c r="R48" s="130"/>
-      <c r="S48" s="130"/>
-      <c r="T48" s="130"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="76"/>
+      <c r="M48" s="76"/>
+      <c r="N48" s="76"/>
+      <c r="O48" s="76"/>
+      <c r="P48" s="76"/>
+      <c r="Q48" s="76"/>
+      <c r="R48" s="76"/>
+      <c r="S48" s="76"/>
+      <c r="T48" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="B48:T48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:S40"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="I46:S46"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="O44:S44"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="I37:S37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="I21:K21"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L25:M25"/>
@@ -3011,6 +2945,72 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="I37:S37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="B48:T48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:S40"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="I46:S46"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="O44:S44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>
